--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TEACH\Aptech\NodeJS\batch-33\batch-33-nodejs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TEACH\Batch-2\NODEJS\CODE\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>

--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="207">
   <si>
     <t>No.</t>
   </si>
@@ -635,6 +635,24 @@
   </si>
   <si>
     <t>Hiển thị tất cả các đơn hàng có trạng thái là &lt;status&gt; có ngày tạo ngoài khoảng &lt;fromDate&gt; và &lt;toDate&gt;</t>
+  </si>
+  <si>
+    <t>3a</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= X</t>
+  </si>
+  <si>
+    <t>3c</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= 1000, sử dụng aggregate thay vì find</t>
+  </si>
+  <si>
+    <t>3d</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= X sử dụng aggregate thay vì find</t>
   </si>
 </sst>
 </file>
@@ -28475,7 +28493,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1014"/>
+  <dimension ref="A1:Z1017"/>
   <sheetFormatPr defaultColWidth="14.3828125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4" style="176" bestFit="1" customWidth="1"/>
@@ -28986,15 +29004,15 @@
       <c r="Z15" s="54"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="173">
-        <v>4</v>
-      </c>
-      <c r="B16" s="165" t="s">
-        <v>54</v>
+      <c r="A16" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="B16" s="164" t="s">
+        <v>202</v>
       </c>
       <c r="C16" s="170"/>
       <c r="D16" s="170" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E16" s="170"/>
       <c r="F16" s="54"/>
@@ -29020,15 +29038,15 @@
       <c r="Z16" s="54"/>
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="173">
-        <v>5</v>
-      </c>
-      <c r="B17" s="165" t="s">
-        <v>55</v>
+      <c r="A17" s="85" t="s">
+        <v>203</v>
+      </c>
+      <c r="B17" s="164" t="s">
+        <v>204</v>
       </c>
       <c r="C17" s="170"/>
       <c r="D17" s="170" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E17" s="170"/>
       <c r="F17" s="54"/>
@@ -29054,15 +29072,15 @@
       <c r="Z17" s="54"/>
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="173" t="s">
-        <v>198</v>
-      </c>
-      <c r="B18" s="165" t="s">
-        <v>197</v>
+      <c r="A18" s="85" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18" s="164" t="s">
+        <v>206</v>
       </c>
       <c r="C18" s="170"/>
       <c r="D18" s="170" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E18" s="170"/>
       <c r="F18" s="54"/>
@@ -29089,10 +29107,10 @@
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="173">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B19" s="165" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" s="170"/>
       <c r="D19" s="170" t="s">
@@ -29122,15 +29140,15 @@
       <c r="Z19" s="54"/>
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="75">
-        <v>7</v>
-      </c>
-      <c r="B20" s="166" t="s">
-        <v>57</v>
+      <c r="A20" s="173">
+        <v>5</v>
+      </c>
+      <c r="B20" s="165" t="s">
+        <v>55</v>
       </c>
       <c r="C20" s="170"/>
       <c r="D20" s="170" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E20" s="170"/>
       <c r="F20" s="54"/>
@@ -29155,16 +29173,16 @@
       <c r="Y20" s="54"/>
       <c r="Z20" s="54"/>
     </row>
-    <row r="21" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A21" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="B21" s="166" t="s">
-        <v>58</v>
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="173" t="s">
+        <v>198</v>
+      </c>
+      <c r="B21" s="165" t="s">
+        <v>197</v>
       </c>
       <c r="C21" s="170"/>
       <c r="D21" s="170" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E21" s="170"/>
       <c r="F21" s="54"/>
@@ -29189,16 +29207,16 @@
       <c r="Y21" s="54"/>
       <c r="Z21" s="54"/>
     </row>
-    <row r="22" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A22" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="B22" s="166" t="s">
-        <v>162</v>
+    <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="173">
+        <v>6</v>
+      </c>
+      <c r="B22" s="165" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="170"/>
       <c r="D22" s="170" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E22" s="170"/>
       <c r="F22" s="54"/>
@@ -29223,12 +29241,12 @@
       <c r="Y22" s="54"/>
       <c r="Z22" s="54"/>
     </row>
-    <row r="23" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A23" s="75" t="s">
-        <v>199</v>
+    <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="75">
+        <v>7</v>
       </c>
       <c r="B23" s="166" t="s">
-        <v>200</v>
+        <v>57</v>
       </c>
       <c r="C23" s="170"/>
       <c r="D23" s="170" t="s">
@@ -29258,11 +29276,11 @@
       <c r="Z23" s="54"/>
     </row>
     <row r="24" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A24" s="75">
-        <v>9</v>
-      </c>
-      <c r="B24" s="167" t="s">
-        <v>59</v>
+      <c r="A24" s="75" t="s">
+        <v>184</v>
+      </c>
+      <c r="B24" s="166" t="s">
+        <v>58</v>
       </c>
       <c r="C24" s="170"/>
       <c r="D24" s="170" t="s">
@@ -29292,11 +29310,11 @@
       <c r="Z24" s="54"/>
     </row>
     <row r="25" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A25" s="75">
-        <v>10</v>
+      <c r="A25" s="75" t="s">
+        <v>185</v>
       </c>
       <c r="B25" s="166" t="s">
-        <v>60</v>
+        <v>162</v>
       </c>
       <c r="C25" s="170"/>
       <c r="D25" s="170" t="s">
@@ -29326,11 +29344,11 @@
       <c r="Z25" s="54"/>
     </row>
     <row r="26" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A26" s="75">
-        <v>11</v>
+      <c r="A26" s="75" t="s">
+        <v>199</v>
       </c>
       <c r="B26" s="166" t="s">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c r="C26" s="170"/>
       <c r="D26" s="170" t="s">
@@ -29361,10 +29379,10 @@
     </row>
     <row r="27" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A27" s="75">
-        <v>12</v>
-      </c>
-      <c r="B27" s="166" t="s">
-        <v>62</v>
+        <v>9</v>
+      </c>
+      <c r="B27" s="167" t="s">
+        <v>59</v>
       </c>
       <c r="C27" s="170"/>
       <c r="D27" s="170" t="s">
@@ -29395,10 +29413,10 @@
     </row>
     <row r="28" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A28" s="75">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B28" s="166" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C28" s="170"/>
       <c r="D28" s="170" t="s">
@@ -29428,15 +29446,15 @@
       <c r="Z28" s="54"/>
     </row>
     <row r="29" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A29" s="174">
-        <v>14</v>
-      </c>
-      <c r="B29" s="168" t="s">
-        <v>64</v>
+      <c r="A29" s="75">
+        <v>11</v>
+      </c>
+      <c r="B29" s="166" t="s">
+        <v>61</v>
       </c>
       <c r="C29" s="170"/>
       <c r="D29" s="170" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E29" s="170"/>
       <c r="F29" s="54"/>
@@ -29462,19 +29480,17 @@
       <c r="Z29" s="54"/>
     </row>
     <row r="30" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A30" s="174">
-        <v>15</v>
-      </c>
-      <c r="B30" s="168" t="s">
-        <v>88</v>
+      <c r="A30" s="75">
+        <v>12</v>
+      </c>
+      <c r="B30" s="166" t="s">
+        <v>62</v>
       </c>
       <c r="C30" s="170"/>
       <c r="D30" s="170" t="s">
-        <v>102</v>
-      </c>
-      <c r="E30" s="170" t="s">
-        <v>122</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="E30" s="170"/>
       <c r="F30" s="54"/>
       <c r="G30" s="54"/>
       <c r="H30" s="54"/>
@@ -29498,11 +29514,11 @@
       <c r="Z30" s="54"/>
     </row>
     <row r="31" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A31" s="174">
-        <v>16</v>
-      </c>
-      <c r="B31" s="168" t="s">
-        <v>65</v>
+      <c r="A31" s="75">
+        <v>13</v>
+      </c>
+      <c r="B31" s="166" t="s">
+        <v>63</v>
       </c>
       <c r="C31" s="170"/>
       <c r="D31" s="170" t="s">
@@ -29533,14 +29549,14 @@
     </row>
     <row r="32" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A32" s="174">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B32" s="168" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C32" s="170"/>
       <c r="D32" s="170" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E32" s="170"/>
       <c r="F32" s="54"/>
@@ -29567,16 +29583,18 @@
     </row>
     <row r="33" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A33" s="174">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B33" s="168" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C33" s="170"/>
       <c r="D33" s="170" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" s="170"/>
+        <v>102</v>
+      </c>
+      <c r="E33" s="170" t="s">
+        <v>122</v>
+      </c>
       <c r="F33" s="54"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
@@ -29601,14 +29619,14 @@
     </row>
     <row r="34" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A34" s="174">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B34" s="168" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34" s="170"/>
       <c r="D34" s="170" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E34" s="170"/>
       <c r="F34" s="54"/>
@@ -29635,14 +29653,14 @@
     </row>
     <row r="35" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A35" s="174">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B35" s="168" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C35" s="170"/>
       <c r="D35" s="170" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E35" s="170"/>
       <c r="F35" s="54"/>
@@ -29667,47 +29685,51 @@
       <c r="Y35" s="54"/>
       <c r="Z35" s="54"/>
     </row>
-    <row r="36" spans="1:26" s="73" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A36" s="188">
-        <v>21</v>
-      </c>
-      <c r="B36" s="189" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="190"/>
-      <c r="D36" s="190"/>
-      <c r="E36" s="190"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
-      <c r="M36" s="111"/>
-      <c r="N36" s="111"/>
-      <c r="O36" s="111"/>
-      <c r="P36" s="111"/>
-      <c r="Q36" s="111"/>
-      <c r="R36" s="111"/>
-      <c r="S36" s="111"/>
-      <c r="T36" s="111"/>
-      <c r="U36" s="111"/>
-      <c r="V36" s="111"/>
-      <c r="W36" s="111"/>
-      <c r="X36" s="111"/>
-      <c r="Y36" s="111"/>
-      <c r="Z36" s="111"/>
+    <row r="36" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A36" s="174">
+        <v>18</v>
+      </c>
+      <c r="B36" s="168" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="170"/>
+      <c r="D36" s="170" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="170"/>
+      <c r="F36" s="54"/>
+      <c r="G36" s="54"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
+      <c r="K36" s="54"/>
+      <c r="L36" s="54"/>
+      <c r="M36" s="54"/>
+      <c r="N36" s="54"/>
+      <c r="O36" s="54"/>
+      <c r="P36" s="54"/>
+      <c r="Q36" s="54"/>
+      <c r="R36" s="54"/>
+      <c r="S36" s="54"/>
+      <c r="T36" s="54"/>
+      <c r="U36" s="54"/>
+      <c r="V36" s="54"/>
+      <c r="W36" s="54"/>
+      <c r="X36" s="54"/>
+      <c r="Y36" s="54"/>
+      <c r="Z36" s="54"/>
     </row>
     <row r="37" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A37" s="174">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B37" s="168" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C37" s="170"/>
-      <c r="D37" s="170"/>
+      <c r="D37" s="170" t="s">
+        <v>102</v>
+      </c>
       <c r="E37" s="170"/>
       <c r="F37" s="54"/>
       <c r="G37" s="54"/>
@@ -29733,13 +29755,15 @@
     </row>
     <row r="38" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A38" s="174">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B38" s="168" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C38" s="170"/>
-      <c r="D38" s="170"/>
+      <c r="D38" s="170" t="s">
+        <v>99</v>
+      </c>
       <c r="E38" s="170"/>
       <c r="F38" s="54"/>
       <c r="G38" s="54"/>
@@ -29763,49 +29787,47 @@
       <c r="Y38" s="54"/>
       <c r="Z38" s="54"/>
     </row>
-    <row r="39" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A39" s="174">
-        <v>24</v>
-      </c>
-      <c r="B39" s="168" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="170"/>
-      <c r="D39" s="170"/>
-      <c r="E39" s="170"/>
-      <c r="F39" s="54"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="54"/>
-      <c r="J39" s="54"/>
-      <c r="K39" s="54"/>
-      <c r="L39" s="54"/>
-      <c r="M39" s="54"/>
-      <c r="N39" s="54"/>
-      <c r="O39" s="54"/>
-      <c r="P39" s="54"/>
-      <c r="Q39" s="54"/>
-      <c r="R39" s="54"/>
-      <c r="S39" s="54"/>
-      <c r="T39" s="54"/>
-      <c r="U39" s="54"/>
-      <c r="V39" s="54"/>
-      <c r="W39" s="54"/>
-      <c r="X39" s="54"/>
-      <c r="Y39" s="54"/>
-      <c r="Z39" s="54"/>
+    <row r="39" spans="1:26" s="73" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A39" s="188">
+        <v>21</v>
+      </c>
+      <c r="B39" s="189" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="190"/>
+      <c r="D39" s="190"/>
+      <c r="E39" s="190"/>
+      <c r="F39" s="111"/>
+      <c r="G39" s="111"/>
+      <c r="H39" s="111"/>
+      <c r="I39" s="111"/>
+      <c r="J39" s="111"/>
+      <c r="K39" s="111"/>
+      <c r="L39" s="111"/>
+      <c r="M39" s="111"/>
+      <c r="N39" s="111"/>
+      <c r="O39" s="111"/>
+      <c r="P39" s="111"/>
+      <c r="Q39" s="111"/>
+      <c r="R39" s="111"/>
+      <c r="S39" s="111"/>
+      <c r="T39" s="111"/>
+      <c r="U39" s="111"/>
+      <c r="V39" s="111"/>
+      <c r="W39" s="111"/>
+      <c r="X39" s="111"/>
+      <c r="Y39" s="111"/>
+      <c r="Z39" s="111"/>
     </row>
     <row r="40" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A40" s="174">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B40" s="168" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C40" s="170"/>
-      <c r="D40" s="170" t="s">
-        <v>100</v>
-      </c>
+      <c r="D40" s="170"/>
       <c r="E40" s="170"/>
       <c r="F40" s="54"/>
       <c r="G40" s="54"/>
@@ -29831,15 +29853,13 @@
     </row>
     <row r="41" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A41" s="174">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B41" s="168" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C41" s="170"/>
-      <c r="D41" s="170" t="s">
-        <v>100</v>
-      </c>
+      <c r="D41" s="170"/>
       <c r="E41" s="170"/>
       <c r="F41" s="54"/>
       <c r="G41" s="54"/>
@@ -29865,16 +29885,14 @@
     </row>
     <row r="42" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A42" s="174">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B42" s="168" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C42" s="170"/>
       <c r="D42" s="170"/>
-      <c r="E42" s="170" t="s">
-        <v>170</v>
-      </c>
+      <c r="E42" s="170"/>
       <c r="F42" s="54"/>
       <c r="G42" s="54"/>
       <c r="H42" s="54"/>
@@ -29899,13 +29917,15 @@
     </row>
     <row r="43" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A43" s="174">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B43" s="168" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C43" s="170"/>
-      <c r="D43" s="170"/>
+      <c r="D43" s="170" t="s">
+        <v>100</v>
+      </c>
       <c r="E43" s="170"/>
       <c r="F43" s="54"/>
       <c r="G43" s="54"/>
@@ -29931,16 +29951,16 @@
     </row>
     <row r="44" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A44" s="174">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B44" s="168" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C44" s="170"/>
-      <c r="D44" s="170"/>
-      <c r="E44" s="170" t="s">
-        <v>171</v>
-      </c>
+      <c r="D44" s="170" t="s">
+        <v>100</v>
+      </c>
+      <c r="E44" s="170"/>
       <c r="F44" s="54"/>
       <c r="G44" s="54"/>
       <c r="H44" s="54"/>
@@ -29965,15 +29985,15 @@
     </row>
     <row r="45" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A45" s="174">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B45" s="168" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C45" s="170"/>
       <c r="D45" s="170"/>
       <c r="E45" s="170" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F45" s="54"/>
       <c r="G45" s="54"/>
@@ -29999,10 +30019,10 @@
     </row>
     <row r="46" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A46" s="174">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B46" s="168" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C46" s="170"/>
       <c r="D46" s="170"/>
@@ -30031,14 +30051,16 @@
     </row>
     <row r="47" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A47" s="174">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B47" s="168" t="s">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="C47" s="170"/>
       <c r="D47" s="170"/>
-      <c r="E47" s="170"/>
+      <c r="E47" s="170" t="s">
+        <v>171</v>
+      </c>
       <c r="F47" s="54"/>
       <c r="G47" s="54"/>
       <c r="H47" s="54"/>
@@ -30063,14 +30085,16 @@
     </row>
     <row r="48" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A48" s="174">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B48" s="168" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C48" s="170"/>
       <c r="D48" s="170"/>
-      <c r="E48" s="170"/>
+      <c r="E48" s="170" t="s">
+        <v>172</v>
+      </c>
       <c r="F48" s="54"/>
       <c r="G48" s="54"/>
       <c r="H48" s="54"/>
@@ -30095,10 +30119,10 @@
     </row>
     <row r="49" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A49" s="174">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B49" s="168" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C49" s="170"/>
       <c r="D49" s="170"/>
@@ -30126,11 +30150,15 @@
       <c r="Z49" s="54"/>
     </row>
     <row r="50" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A50" s="175"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="54"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="54"/>
+      <c r="A50" s="174">
+        <v>32</v>
+      </c>
+      <c r="B50" s="168" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50" s="170"/>
+      <c r="D50" s="170"/>
+      <c r="E50" s="170"/>
       <c r="F50" s="54"/>
       <c r="G50" s="54"/>
       <c r="H50" s="54"/>
@@ -30154,11 +30182,15 @@
       <c r="Z50" s="54"/>
     </row>
     <row r="51" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A51" s="175"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
+      <c r="A51" s="174">
+        <v>33</v>
+      </c>
+      <c r="B51" s="168" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" s="170"/>
+      <c r="D51" s="170"/>
+      <c r="E51" s="170"/>
       <c r="F51" s="54"/>
       <c r="G51" s="54"/>
       <c r="H51" s="54"/>
@@ -30182,11 +30214,15 @@
       <c r="Z51" s="54"/>
     </row>
     <row r="52" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A52" s="175"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
+      <c r="A52" s="174">
+        <v>34</v>
+      </c>
+      <c r="B52" s="168" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" s="170"/>
+      <c r="D52" s="170"/>
+      <c r="E52" s="170"/>
       <c r="F52" s="54"/>
       <c r="G52" s="54"/>
       <c r="H52" s="54"/>
@@ -57145,6 +57181,90 @@
       <c r="Y1014" s="54"/>
       <c r="Z1014" s="54"/>
     </row>
+    <row r="1015" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A1015" s="175"/>
+      <c r="B1015" s="54"/>
+      <c r="C1015" s="54"/>
+      <c r="D1015" s="54"/>
+      <c r="E1015" s="54"/>
+      <c r="F1015" s="54"/>
+      <c r="G1015" s="54"/>
+      <c r="H1015" s="54"/>
+      <c r="I1015" s="54"/>
+      <c r="J1015" s="54"/>
+      <c r="K1015" s="54"/>
+      <c r="L1015" s="54"/>
+      <c r="M1015" s="54"/>
+      <c r="N1015" s="54"/>
+      <c r="O1015" s="54"/>
+      <c r="P1015" s="54"/>
+      <c r="Q1015" s="54"/>
+      <c r="R1015" s="54"/>
+      <c r="S1015" s="54"/>
+      <c r="T1015" s="54"/>
+      <c r="U1015" s="54"/>
+      <c r="V1015" s="54"/>
+      <c r="W1015" s="54"/>
+      <c r="X1015" s="54"/>
+      <c r="Y1015" s="54"/>
+      <c r="Z1015" s="54"/>
+    </row>
+    <row r="1016" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A1016" s="175"/>
+      <c r="B1016" s="54"/>
+      <c r="C1016" s="54"/>
+      <c r="D1016" s="54"/>
+      <c r="E1016" s="54"/>
+      <c r="F1016" s="54"/>
+      <c r="G1016" s="54"/>
+      <c r="H1016" s="54"/>
+      <c r="I1016" s="54"/>
+      <c r="J1016" s="54"/>
+      <c r="K1016" s="54"/>
+      <c r="L1016" s="54"/>
+      <c r="M1016" s="54"/>
+      <c r="N1016" s="54"/>
+      <c r="O1016" s="54"/>
+      <c r="P1016" s="54"/>
+      <c r="Q1016" s="54"/>
+      <c r="R1016" s="54"/>
+      <c r="S1016" s="54"/>
+      <c r="T1016" s="54"/>
+      <c r="U1016" s="54"/>
+      <c r="V1016" s="54"/>
+      <c r="W1016" s="54"/>
+      <c r="X1016" s="54"/>
+      <c r="Y1016" s="54"/>
+      <c r="Z1016" s="54"/>
+    </row>
+    <row r="1017" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A1017" s="175"/>
+      <c r="B1017" s="54"/>
+      <c r="C1017" s="54"/>
+      <c r="D1017" s="54"/>
+      <c r="E1017" s="54"/>
+      <c r="F1017" s="54"/>
+      <c r="G1017" s="54"/>
+      <c r="H1017" s="54"/>
+      <c r="I1017" s="54"/>
+      <c r="J1017" s="54"/>
+      <c r="K1017" s="54"/>
+      <c r="L1017" s="54"/>
+      <c r="M1017" s="54"/>
+      <c r="N1017" s="54"/>
+      <c r="O1017" s="54"/>
+      <c r="P1017" s="54"/>
+      <c r="Q1017" s="54"/>
+      <c r="R1017" s="54"/>
+      <c r="S1017" s="54"/>
+      <c r="T1017" s="54"/>
+      <c r="U1017" s="54"/>
+      <c r="V1017" s="54"/>
+      <c r="W1017" s="54"/>
+      <c r="X1017" s="54"/>
+      <c r="Y1017" s="54"/>
+      <c r="Z1017" s="54"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="209">
   <si>
     <t>No.</t>
   </si>
@@ -646,20 +646,26 @@
     <t>3c</t>
   </si>
   <si>
-    <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= 1000, sử dụng aggregate thay vì find</t>
-  </si>
-  <si>
     <t>3d</t>
   </si>
   <si>
-    <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= X sử dụng aggregate thay vì find</t>
+    <t>3e</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= 1000, Sử dụng aggregate và thêm trường mới và lựa chọn field dữ liệu trả về và thông tin danh mục, nhà cung cấp</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= 1000, Sử dụng aggregate và thêm trường mới và lựa chọn field dữ liệu trả về</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= 1000, Sử dụng aggregate</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -795,6 +801,12 @@
       <i/>
       <sz val="11"/>
       <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1035,7 +1047,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="201">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1483,6 +1495,15 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -28493,7 +28514,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1017"/>
+  <dimension ref="A1:Z1018"/>
   <sheetFormatPr defaultColWidth="14.3828125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4" style="176" bestFit="1" customWidth="1"/>
@@ -29042,7 +29063,7 @@
         <v>203</v>
       </c>
       <c r="B17" s="164" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C17" s="170"/>
       <c r="D17" s="170" t="s">
@@ -29073,10 +29094,10 @@
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="85" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B18" s="164" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="170"/>
       <c r="D18" s="170" t="s">
@@ -29106,15 +29127,15 @@
       <c r="Z18" s="54"/>
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="173">
-        <v>4</v>
-      </c>
-      <c r="B19" s="165" t="s">
-        <v>54</v>
+      <c r="A19" s="85" t="s">
+        <v>205</v>
+      </c>
+      <c r="B19" s="164" t="s">
+        <v>206</v>
       </c>
       <c r="C19" s="170"/>
       <c r="D19" s="170" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E19" s="170"/>
       <c r="F19" s="54"/>
@@ -29141,10 +29162,10 @@
     </row>
     <row r="20" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" s="165" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C20" s="170"/>
       <c r="D20" s="170" t="s">
@@ -29174,11 +29195,11 @@
       <c r="Z20" s="54"/>
     </row>
     <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="173" t="s">
-        <v>198</v>
+      <c r="A21" s="173">
+        <v>5</v>
       </c>
       <c r="B21" s="165" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="C21" s="170"/>
       <c r="D21" s="170" t="s">
@@ -29208,11 +29229,11 @@
       <c r="Z21" s="54"/>
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="173">
-        <v>6</v>
+      <c r="A22" s="173" t="s">
+        <v>198</v>
       </c>
       <c r="B22" s="165" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="C22" s="170"/>
       <c r="D22" s="170" t="s">
@@ -29242,15 +29263,15 @@
       <c r="Z22" s="54"/>
     </row>
     <row r="23" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="75">
-        <v>7</v>
-      </c>
-      <c r="B23" s="166" t="s">
-        <v>57</v>
+      <c r="A23" s="173">
+        <v>6</v>
+      </c>
+      <c r="B23" s="165" t="s">
+        <v>56</v>
       </c>
       <c r="C23" s="170"/>
       <c r="D23" s="170" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E23" s="170"/>
       <c r="F23" s="54"/>
@@ -29275,12 +29296,12 @@
       <c r="Y23" s="54"/>
       <c r="Z23" s="54"/>
     </row>
-    <row r="24" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A24" s="75" t="s">
-        <v>184</v>
+    <row r="24" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="75">
+        <v>7</v>
       </c>
       <c r="B24" s="166" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C24" s="170"/>
       <c r="D24" s="170" t="s">
@@ -29311,10 +29332,10 @@
     </row>
     <row r="25" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A25" s="75" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B25" s="166" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="C25" s="170"/>
       <c r="D25" s="170" t="s">
@@ -29345,10 +29366,10 @@
     </row>
     <row r="26" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A26" s="75" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B26" s="166" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="C26" s="170"/>
       <c r="D26" s="170" t="s">
@@ -29378,11 +29399,11 @@
       <c r="Z26" s="54"/>
     </row>
     <row r="27" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A27" s="75">
-        <v>9</v>
-      </c>
-      <c r="B27" s="167" t="s">
-        <v>59</v>
+      <c r="A27" s="75" t="s">
+        <v>199</v>
+      </c>
+      <c r="B27" s="166" t="s">
+        <v>200</v>
       </c>
       <c r="C27" s="170"/>
       <c r="D27" s="170" t="s">
@@ -29413,10 +29434,10 @@
     </row>
     <row r="28" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A28" s="75">
-        <v>10</v>
-      </c>
-      <c r="B28" s="166" t="s">
-        <v>60</v>
+        <v>9</v>
+      </c>
+      <c r="B28" s="167" t="s">
+        <v>59</v>
       </c>
       <c r="C28" s="170"/>
       <c r="D28" s="170" t="s">
@@ -29447,10 +29468,10 @@
     </row>
     <row r="29" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A29" s="75">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="166" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="170"/>
       <c r="D29" s="170" t="s">
@@ -29481,10 +29502,10 @@
     </row>
     <row r="30" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A30" s="75">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" s="166" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="170"/>
       <c r="D30" s="170" t="s">
@@ -29515,10 +29536,10 @@
     </row>
     <row r="31" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A31" s="75">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" s="166" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="170"/>
       <c r="D31" s="170" t="s">
@@ -29548,15 +29569,15 @@
       <c r="Z31" s="54"/>
     </row>
     <row r="32" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A32" s="174">
-        <v>14</v>
-      </c>
-      <c r="B32" s="168" t="s">
-        <v>64</v>
+      <c r="A32" s="75">
+        <v>13</v>
+      </c>
+      <c r="B32" s="166" t="s">
+        <v>63</v>
       </c>
       <c r="C32" s="170"/>
       <c r="D32" s="170" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E32" s="170"/>
       <c r="F32" s="54"/>
@@ -29583,18 +29604,16 @@
     </row>
     <row r="33" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A33" s="174">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" s="168" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C33" s="170"/>
       <c r="D33" s="170" t="s">
-        <v>102</v>
-      </c>
-      <c r="E33" s="170" t="s">
-        <v>122</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="E33" s="170"/>
       <c r="F33" s="54"/>
       <c r="G33" s="54"/>
       <c r="H33" s="54"/>
@@ -29619,16 +29638,18 @@
     </row>
     <row r="34" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A34" s="174">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" s="168" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="C34" s="170"/>
       <c r="D34" s="170" t="s">
-        <v>99</v>
-      </c>
-      <c r="E34" s="170"/>
+        <v>102</v>
+      </c>
+      <c r="E34" s="170" t="s">
+        <v>122</v>
+      </c>
       <c r="F34" s="54"/>
       <c r="G34" s="54"/>
       <c r="H34" s="54"/>
@@ -29653,14 +29674,14 @@
     </row>
     <row r="35" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A35" s="174">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35" s="168" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35" s="170"/>
       <c r="D35" s="170" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E35" s="170"/>
       <c r="F35" s="54"/>
@@ -29687,14 +29708,14 @@
     </row>
     <row r="36" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A36" s="174">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" s="168" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C36" s="170"/>
       <c r="D36" s="170" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E36" s="170"/>
       <c r="F36" s="54"/>
@@ -29721,14 +29742,14 @@
     </row>
     <row r="37" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A37" s="174">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" s="168" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C37" s="170"/>
       <c r="D37" s="170" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E37" s="170"/>
       <c r="F37" s="54"/>
@@ -29755,14 +29776,14 @@
     </row>
     <row r="38" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A38" s="174">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" s="168" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C38" s="170"/>
       <c r="D38" s="170" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E38" s="170"/>
       <c r="F38" s="54"/>
@@ -29787,76 +29808,78 @@
       <c r="Y38" s="54"/>
       <c r="Z38" s="54"/>
     </row>
-    <row r="39" spans="1:26" s="73" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A39" s="188">
+    <row r="39" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A39" s="174">
+        <v>20</v>
+      </c>
+      <c r="B39" s="168" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="170"/>
+      <c r="D39" s="170" t="s">
+        <v>99</v>
+      </c>
+      <c r="E39" s="170"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="54"/>
+      <c r="K39" s="54"/>
+      <c r="L39" s="54"/>
+      <c r="M39" s="54"/>
+      <c r="N39" s="54"/>
+      <c r="O39" s="54"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="54"/>
+      <c r="R39" s="54"/>
+      <c r="S39" s="54"/>
+      <c r="T39" s="54"/>
+      <c r="U39" s="54"/>
+      <c r="V39" s="54"/>
+      <c r="W39" s="54"/>
+      <c r="X39" s="54"/>
+      <c r="Y39" s="54"/>
+      <c r="Z39" s="54"/>
+    </row>
+    <row r="40" spans="1:26" s="73" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A40" s="188">
         <v>21</v>
       </c>
-      <c r="B39" s="189" t="s">
+      <c r="B40" s="189" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="190"/>
-      <c r="D39" s="190"/>
-      <c r="E39" s="190"/>
-      <c r="F39" s="111"/>
-      <c r="G39" s="111"/>
-      <c r="H39" s="111"/>
-      <c r="I39" s="111"/>
-      <c r="J39" s="111"/>
-      <c r="K39" s="111"/>
-      <c r="L39" s="111"/>
-      <c r="M39" s="111"/>
-      <c r="N39" s="111"/>
-      <c r="O39" s="111"/>
-      <c r="P39" s="111"/>
-      <c r="Q39" s="111"/>
-      <c r="R39" s="111"/>
-      <c r="S39" s="111"/>
-      <c r="T39" s="111"/>
-      <c r="U39" s="111"/>
-      <c r="V39" s="111"/>
-      <c r="W39" s="111"/>
-      <c r="X39" s="111"/>
-      <c r="Y39" s="111"/>
-      <c r="Z39" s="111"/>
-    </row>
-    <row r="40" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A40" s="174">
-        <v>22</v>
-      </c>
-      <c r="B40" s="168" t="s">
-        <v>71</v>
-      </c>
-      <c r="C40" s="170"/>
-      <c r="D40" s="170"/>
-      <c r="E40" s="170"/>
-      <c r="F40" s="54"/>
-      <c r="G40" s="54"/>
-      <c r="H40" s="54"/>
-      <c r="I40" s="54"/>
-      <c r="J40" s="54"/>
-      <c r="K40" s="54"/>
-      <c r="L40" s="54"/>
-      <c r="M40" s="54"/>
-      <c r="N40" s="54"/>
-      <c r="O40" s="54"/>
-      <c r="P40" s="54"/>
-      <c r="Q40" s="54"/>
-      <c r="R40" s="54"/>
-      <c r="S40" s="54"/>
-      <c r="T40" s="54"/>
-      <c r="U40" s="54"/>
-      <c r="V40" s="54"/>
-      <c r="W40" s="54"/>
-      <c r="X40" s="54"/>
-      <c r="Y40" s="54"/>
-      <c r="Z40" s="54"/>
+      <c r="C40" s="190"/>
+      <c r="D40" s="190"/>
+      <c r="E40" s="190"/>
+      <c r="F40" s="111"/>
+      <c r="G40" s="111"/>
+      <c r="H40" s="111"/>
+      <c r="I40" s="111"/>
+      <c r="J40" s="111"/>
+      <c r="K40" s="111"/>
+      <c r="L40" s="111"/>
+      <c r="M40" s="111"/>
+      <c r="N40" s="111"/>
+      <c r="O40" s="111"/>
+      <c r="P40" s="111"/>
+      <c r="Q40" s="111"/>
+      <c r="R40" s="111"/>
+      <c r="S40" s="111"/>
+      <c r="T40" s="111"/>
+      <c r="U40" s="111"/>
+      <c r="V40" s="111"/>
+      <c r="W40" s="111"/>
+      <c r="X40" s="111"/>
+      <c r="Y40" s="111"/>
+      <c r="Z40" s="111"/>
     </row>
     <row r="41" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A41" s="174">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" s="168" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C41" s="170"/>
       <c r="D41" s="170"/>
@@ -29885,10 +29908,10 @@
     </row>
     <row r="42" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A42" s="174">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" s="168" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C42" s="170"/>
       <c r="D42" s="170"/>
@@ -29917,15 +29940,13 @@
     </row>
     <row r="43" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A43" s="174">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" s="168" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C43" s="170"/>
-      <c r="D43" s="170" t="s">
-        <v>100</v>
-      </c>
+      <c r="D43" s="170"/>
       <c r="E43" s="170"/>
       <c r="F43" s="54"/>
       <c r="G43" s="54"/>
@@ -29951,10 +29972,10 @@
     </row>
     <row r="44" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A44" s="174">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" s="168" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C44" s="170"/>
       <c r="D44" s="170" t="s">
@@ -29983,50 +30004,52 @@
       <c r="Y44" s="54"/>
       <c r="Z44" s="54"/>
     </row>
-    <row r="45" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A45" s="174">
-        <v>27</v>
-      </c>
-      <c r="B45" s="168" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" s="170"/>
-      <c r="D45" s="170"/>
-      <c r="E45" s="170" t="s">
-        <v>170</v>
-      </c>
-      <c r="F45" s="54"/>
-      <c r="G45" s="54"/>
-      <c r="H45" s="54"/>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="54"/>
-      <c r="L45" s="54"/>
-      <c r="M45" s="54"/>
-      <c r="N45" s="54"/>
-      <c r="O45" s="54"/>
-      <c r="P45" s="54"/>
-      <c r="Q45" s="54"/>
-      <c r="R45" s="54"/>
-      <c r="S45" s="54"/>
-      <c r="T45" s="54"/>
-      <c r="U45" s="54"/>
-      <c r="V45" s="54"/>
-      <c r="W45" s="54"/>
-      <c r="X45" s="54"/>
-      <c r="Y45" s="54"/>
-      <c r="Z45" s="54"/>
+    <row r="45" spans="1:26" s="205" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A45" s="201">
+        <v>26</v>
+      </c>
+      <c r="B45" s="202" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="203"/>
+      <c r="D45" s="203" t="s">
+        <v>100</v>
+      </c>
+      <c r="E45" s="203"/>
+      <c r="F45" s="204"/>
+      <c r="G45" s="204"/>
+      <c r="H45" s="204"/>
+      <c r="I45" s="204"/>
+      <c r="J45" s="204"/>
+      <c r="K45" s="204"/>
+      <c r="L45" s="204"/>
+      <c r="M45" s="204"/>
+      <c r="N45" s="204"/>
+      <c r="O45" s="204"/>
+      <c r="P45" s="204"/>
+      <c r="Q45" s="204"/>
+      <c r="R45" s="204"/>
+      <c r="S45" s="204"/>
+      <c r="T45" s="204"/>
+      <c r="U45" s="204"/>
+      <c r="V45" s="204"/>
+      <c r="W45" s="204"/>
+      <c r="X45" s="204"/>
+      <c r="Y45" s="204"/>
+      <c r="Z45" s="204"/>
     </row>
     <row r="46" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A46" s="174">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" s="168" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C46" s="170"/>
       <c r="D46" s="170"/>
-      <c r="E46" s="170"/>
+      <c r="E46" s="170" t="s">
+        <v>170</v>
+      </c>
       <c r="F46" s="54"/>
       <c r="G46" s="54"/>
       <c r="H46" s="54"/>
@@ -30051,16 +30074,14 @@
     </row>
     <row r="47" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A47" s="174">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" s="168" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C47" s="170"/>
       <c r="D47" s="170"/>
-      <c r="E47" s="170" t="s">
-        <v>171</v>
-      </c>
+      <c r="E47" s="170"/>
       <c r="F47" s="54"/>
       <c r="G47" s="54"/>
       <c r="H47" s="54"/>
@@ -30085,15 +30106,15 @@
     </row>
     <row r="48" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A48" s="174">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B48" s="168" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C48" s="170"/>
       <c r="D48" s="170"/>
       <c r="E48" s="170" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" s="54"/>
       <c r="G48" s="54"/>
@@ -30119,14 +30140,16 @@
     </row>
     <row r="49" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A49" s="174">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B49" s="168" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C49" s="170"/>
       <c r="D49" s="170"/>
-      <c r="E49" s="170"/>
+      <c r="E49" s="170" t="s">
+        <v>172</v>
+      </c>
       <c r="F49" s="54"/>
       <c r="G49" s="54"/>
       <c r="H49" s="54"/>
@@ -30151,10 +30174,10 @@
     </row>
     <row r="50" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A50" s="174">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B50" s="168" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="C50" s="170"/>
       <c r="D50" s="170"/>
@@ -30183,10 +30206,10 @@
     </row>
     <row r="51" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A51" s="174">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B51" s="168" t="s">
-        <v>81</v>
+        <v>173</v>
       </c>
       <c r="C51" s="170"/>
       <c r="D51" s="170"/>
@@ -30215,10 +30238,10 @@
     </row>
     <row r="52" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A52" s="174">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B52" s="168" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C52" s="170"/>
       <c r="D52" s="170"/>
@@ -30246,11 +30269,15 @@
       <c r="Z52" s="54"/>
     </row>
     <row r="53" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A53" s="175"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="54"/>
-      <c r="D53" s="54"/>
-      <c r="E53" s="54"/>
+      <c r="A53" s="174">
+        <v>34</v>
+      </c>
+      <c r="B53" s="168" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" s="170"/>
+      <c r="D53" s="170"/>
+      <c r="E53" s="170"/>
       <c r="F53" s="54"/>
       <c r="G53" s="54"/>
       <c r="H53" s="54"/>
@@ -57265,6 +57292,34 @@
       <c r="Y1017" s="54"/>
       <c r="Z1017" s="54"/>
     </row>
+    <row r="1018" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A1018" s="175"/>
+      <c r="B1018" s="54"/>
+      <c r="C1018" s="54"/>
+      <c r="D1018" s="54"/>
+      <c r="E1018" s="54"/>
+      <c r="F1018" s="54"/>
+      <c r="G1018" s="54"/>
+      <c r="H1018" s="54"/>
+      <c r="I1018" s="54"/>
+      <c r="J1018" s="54"/>
+      <c r="K1018" s="54"/>
+      <c r="L1018" s="54"/>
+      <c r="M1018" s="54"/>
+      <c r="N1018" s="54"/>
+      <c r="O1018" s="54"/>
+      <c r="P1018" s="54"/>
+      <c r="Q1018" s="54"/>
+      <c r="R1018" s="54"/>
+      <c r="S1018" s="54"/>
+      <c r="T1018" s="54"/>
+      <c r="U1018" s="54"/>
+      <c r="V1018" s="54"/>
+      <c r="W1018" s="54"/>
+      <c r="X1018" s="54"/>
+      <c r="Y1018" s="54"/>
+      <c r="Z1018" s="54"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -1469,6 +1469,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1495,15 +1504,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2431,17 +2431,17 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="191" t="s">
+      <c r="A19" s="196" t="s">
         <v>176</v>
       </c>
-      <c r="B19" s="191"/>
-      <c r="C19" s="191"/>
-      <c r="D19" s="191"/>
-      <c r="E19" s="191"/>
-      <c r="F19" s="191"/>
-      <c r="G19" s="191"/>
-      <c r="H19" s="191"/>
-      <c r="I19" s="191"/>
+      <c r="B19" s="196"/>
+      <c r="C19" s="196"/>
+      <c r="D19" s="196"/>
+      <c r="E19" s="196"/>
+      <c r="F19" s="196"/>
+      <c r="G19" s="196"/>
+      <c r="H19" s="196"/>
+      <c r="I19" s="196"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -2757,17 +2757,17 @@
       <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="191" t="s">
+      <c r="A28" s="196" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="191"/>
-      <c r="C28" s="191"/>
-      <c r="D28" s="191"/>
-      <c r="E28" s="191"/>
-      <c r="F28" s="191"/>
-      <c r="G28" s="191"/>
-      <c r="H28" s="191"/>
-      <c r="I28" s="191"/>
+      <c r="B28" s="196"/>
+      <c r="C28" s="196"/>
+      <c r="D28" s="196"/>
+      <c r="E28" s="196"/>
+      <c r="F28" s="196"/>
+      <c r="G28" s="196"/>
+      <c r="H28" s="196"/>
+      <c r="I28" s="196"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -3257,17 +3257,17 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="194" t="s">
+      <c r="A42" s="199" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="195"/>
-      <c r="C42" s="195"/>
-      <c r="D42" s="195"/>
-      <c r="E42" s="195"/>
-      <c r="F42" s="195"/>
-      <c r="G42" s="195"/>
-      <c r="H42" s="195"/>
-      <c r="I42" s="196"/>
+      <c r="B42" s="200"/>
+      <c r="C42" s="200"/>
+      <c r="D42" s="200"/>
+      <c r="E42" s="200"/>
+      <c r="F42" s="200"/>
+      <c r="G42" s="200"/>
+      <c r="H42" s="200"/>
+      <c r="I42" s="201"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -3757,17 +3757,17 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="197" t="s">
+      <c r="A56" s="202" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="197"/>
-      <c r="C56" s="197"/>
-      <c r="D56" s="197"/>
-      <c r="E56" s="197"/>
-      <c r="F56" s="197"/>
-      <c r="G56" s="197"/>
-      <c r="H56" s="197"/>
-      <c r="I56" s="197"/>
+      <c r="B56" s="202"/>
+      <c r="C56" s="202"/>
+      <c r="D56" s="202"/>
+      <c r="E56" s="202"/>
+      <c r="F56" s="202"/>
+      <c r="G56" s="202"/>
+      <c r="H56" s="202"/>
+      <c r="I56" s="202"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -4301,13 +4301,13 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="198" t="s">
+      <c r="A71" s="203" t="s">
         <v>92</v>
       </c>
-      <c r="B71" s="199"/>
-      <c r="C71" s="199"/>
-      <c r="D71" s="199"/>
-      <c r="E71" s="199"/>
+      <c r="B71" s="204"/>
+      <c r="C71" s="204"/>
+      <c r="D71" s="204"/>
+      <c r="E71" s="204"/>
       <c r="F71" s="50"/>
       <c r="G71" s="50"/>
       <c r="H71" s="50"/>
@@ -5007,13 +5007,13 @@
       <c r="Z88" s="77"/>
     </row>
     <row r="89" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="200" t="s">
+      <c r="A89" s="205" t="s">
         <v>93</v>
       </c>
-      <c r="B89" s="199"/>
-      <c r="C89" s="199"/>
-      <c r="D89" s="199"/>
-      <c r="E89" s="199"/>
+      <c r="B89" s="204"/>
+      <c r="C89" s="204"/>
+      <c r="D89" s="204"/>
+      <c r="E89" s="204"/>
       <c r="F89" s="52"/>
       <c r="G89" s="52"/>
       <c r="H89" s="50"/>
@@ -5323,13 +5323,13 @@
       <c r="Z97" s="54"/>
     </row>
     <row r="98" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A98" s="198" t="s">
+      <c r="A98" s="203" t="s">
         <v>187</v>
       </c>
-      <c r="B98" s="199"/>
-      <c r="C98" s="199"/>
-      <c r="D98" s="199"/>
-      <c r="E98" s="199"/>
+      <c r="B98" s="204"/>
+      <c r="C98" s="204"/>
+      <c r="D98" s="204"/>
+      <c r="E98" s="204"/>
       <c r="F98" s="50"/>
       <c r="G98" s="50"/>
       <c r="H98" s="50"/>
@@ -5537,13 +5537,13 @@
       <c r="Z103" s="77"/>
     </row>
     <row r="104" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A104" s="200" t="s">
+      <c r="A104" s="205" t="s">
         <v>190</v>
       </c>
-      <c r="B104" s="199"/>
-      <c r="C104" s="199"/>
-      <c r="D104" s="199"/>
-      <c r="E104" s="199"/>
+      <c r="B104" s="204"/>
+      <c r="C104" s="204"/>
+      <c r="D104" s="204"/>
+      <c r="E104" s="204"/>
       <c r="F104" s="52"/>
       <c r="G104" s="52"/>
       <c r="H104" s="50"/>
@@ -6321,13 +6321,13 @@
       <c r="AJ157" s="77"/>
     </row>
     <row r="158" spans="1:36" s="78" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A158" s="192" t="s">
+      <c r="A158" s="197" t="s">
         <v>108</v>
       </c>
-      <c r="B158" s="193"/>
-      <c r="C158" s="193"/>
-      <c r="D158" s="193"/>
-      <c r="E158" s="193"/>
+      <c r="B158" s="198"/>
+      <c r="C158" s="198"/>
+      <c r="D158" s="198"/>
+      <c r="E158" s="198"/>
       <c r="F158" s="58"/>
       <c r="G158" s="58"/>
       <c r="H158" s="57"/>
@@ -6761,13 +6761,13 @@
       <c r="AJ167" s="77"/>
     </row>
     <row r="168" spans="1:36" s="78" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A168" s="192" t="s">
+      <c r="A168" s="197" t="s">
         <v>113</v>
       </c>
-      <c r="B168" s="193"/>
-      <c r="C168" s="193"/>
-      <c r="D168" s="193"/>
-      <c r="E168" s="193"/>
+      <c r="B168" s="198"/>
+      <c r="C168" s="198"/>
+      <c r="D168" s="198"/>
+      <c r="E168" s="198"/>
       <c r="F168" s="58"/>
       <c r="G168" s="58"/>
       <c r="H168" s="57"/>
@@ -7425,13 +7425,13 @@
       <c r="AJ182" s="77"/>
     </row>
     <row r="183" spans="1:36" s="78" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A183" s="192" t="s">
+      <c r="A183" s="197" t="s">
         <v>132</v>
       </c>
-      <c r="B183" s="193"/>
-      <c r="C183" s="193"/>
-      <c r="D183" s="193"/>
-      <c r="E183" s="193"/>
+      <c r="B183" s="198"/>
+      <c r="C183" s="198"/>
+      <c r="D183" s="198"/>
+      <c r="E183" s="198"/>
       <c r="F183" s="58"/>
       <c r="G183" s="58"/>
       <c r="H183" s="57"/>
@@ -29740,39 +29740,39 @@
       <c r="Y36" s="54"/>
       <c r="Z36" s="54"/>
     </row>
-    <row r="37" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A37" s="174">
+    <row r="37" spans="1:26" s="73" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A37" s="188">
         <v>18</v>
       </c>
-      <c r="B37" s="168" t="s">
+      <c r="B37" s="189" t="s">
         <v>67</v>
       </c>
-      <c r="C37" s="170"/>
-      <c r="D37" s="170" t="s">
+      <c r="C37" s="190"/>
+      <c r="D37" s="190" t="s">
         <v>107</v>
       </c>
-      <c r="E37" s="170"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="54"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="54"/>
-      <c r="L37" s="54"/>
-      <c r="M37" s="54"/>
-      <c r="N37" s="54"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="54"/>
-      <c r="S37" s="54"/>
-      <c r="T37" s="54"/>
-      <c r="U37" s="54"/>
-      <c r="V37" s="54"/>
-      <c r="W37" s="54"/>
-      <c r="X37" s="54"/>
-      <c r="Y37" s="54"/>
-      <c r="Z37" s="54"/>
+      <c r="E37" s="190"/>
+      <c r="F37" s="111"/>
+      <c r="G37" s="111"/>
+      <c r="H37" s="111"/>
+      <c r="I37" s="111"/>
+      <c r="J37" s="111"/>
+      <c r="K37" s="111"/>
+      <c r="L37" s="111"/>
+      <c r="M37" s="111"/>
+      <c r="N37" s="111"/>
+      <c r="O37" s="111"/>
+      <c r="P37" s="111"/>
+      <c r="Q37" s="111"/>
+      <c r="R37" s="111"/>
+      <c r="S37" s="111"/>
+      <c r="T37" s="111"/>
+      <c r="U37" s="111"/>
+      <c r="V37" s="111"/>
+      <c r="W37" s="111"/>
+      <c r="X37" s="111"/>
+      <c r="Y37" s="111"/>
+      <c r="Z37" s="111"/>
     </row>
     <row r="38" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A38" s="174">
@@ -29842,37 +29842,37 @@
       <c r="Y39" s="54"/>
       <c r="Z39" s="54"/>
     </row>
-    <row r="40" spans="1:26" s="73" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A40" s="188">
+    <row r="40" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A40" s="174">
         <v>21</v>
       </c>
-      <c r="B40" s="189" t="s">
+      <c r="B40" s="168" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="190"/>
-      <c r="D40" s="190"/>
-      <c r="E40" s="190"/>
-      <c r="F40" s="111"/>
-      <c r="G40" s="111"/>
-      <c r="H40" s="111"/>
-      <c r="I40" s="111"/>
-      <c r="J40" s="111"/>
-      <c r="K40" s="111"/>
-      <c r="L40" s="111"/>
-      <c r="M40" s="111"/>
-      <c r="N40" s="111"/>
-      <c r="O40" s="111"/>
-      <c r="P40" s="111"/>
-      <c r="Q40" s="111"/>
-      <c r="R40" s="111"/>
-      <c r="S40" s="111"/>
-      <c r="T40" s="111"/>
-      <c r="U40" s="111"/>
-      <c r="V40" s="111"/>
-      <c r="W40" s="111"/>
-      <c r="X40" s="111"/>
-      <c r="Y40" s="111"/>
-      <c r="Z40" s="111"/>
+      <c r="C40" s="170"/>
+      <c r="D40" s="170"/>
+      <c r="E40" s="170"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="54"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="54"/>
+      <c r="K40" s="54"/>
+      <c r="L40" s="54"/>
+      <c r="M40" s="54"/>
+      <c r="N40" s="54"/>
+      <c r="O40" s="54"/>
+      <c r="P40" s="54"/>
+      <c r="Q40" s="54"/>
+      <c r="R40" s="54"/>
+      <c r="S40" s="54"/>
+      <c r="T40" s="54"/>
+      <c r="U40" s="54"/>
+      <c r="V40" s="54"/>
+      <c r="W40" s="54"/>
+      <c r="X40" s="54"/>
+      <c r="Y40" s="54"/>
+      <c r="Z40" s="54"/>
     </row>
     <row r="41" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A41" s="174">
@@ -30004,39 +30004,39 @@
       <c r="Y44" s="54"/>
       <c r="Z44" s="54"/>
     </row>
-    <row r="45" spans="1:26" s="205" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A45" s="201">
+    <row r="45" spans="1:26" s="195" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A45" s="191">
         <v>26</v>
       </c>
-      <c r="B45" s="202" t="s">
+      <c r="B45" s="192" t="s">
         <v>75</v>
       </c>
-      <c r="C45" s="203"/>
-      <c r="D45" s="203" t="s">
+      <c r="C45" s="193"/>
+      <c r="D45" s="193" t="s">
         <v>100</v>
       </c>
-      <c r="E45" s="203"/>
-      <c r="F45" s="204"/>
-      <c r="G45" s="204"/>
-      <c r="H45" s="204"/>
-      <c r="I45" s="204"/>
-      <c r="J45" s="204"/>
-      <c r="K45" s="204"/>
-      <c r="L45" s="204"/>
-      <c r="M45" s="204"/>
-      <c r="N45" s="204"/>
-      <c r="O45" s="204"/>
-      <c r="P45" s="204"/>
-      <c r="Q45" s="204"/>
-      <c r="R45" s="204"/>
-      <c r="S45" s="204"/>
-      <c r="T45" s="204"/>
-      <c r="U45" s="204"/>
-      <c r="V45" s="204"/>
-      <c r="W45" s="204"/>
-      <c r="X45" s="204"/>
-      <c r="Y45" s="204"/>
-      <c r="Z45" s="204"/>
+      <c r="E45" s="193"/>
+      <c r="F45" s="194"/>
+      <c r="G45" s="194"/>
+      <c r="H45" s="194"/>
+      <c r="I45" s="194"/>
+      <c r="J45" s="194"/>
+      <c r="K45" s="194"/>
+      <c r="L45" s="194"/>
+      <c r="M45" s="194"/>
+      <c r="N45" s="194"/>
+      <c r="O45" s="194"/>
+      <c r="P45" s="194"/>
+      <c r="Q45" s="194"/>
+      <c r="R45" s="194"/>
+      <c r="S45" s="194"/>
+      <c r="T45" s="194"/>
+      <c r="U45" s="194"/>
+      <c r="V45" s="194"/>
+      <c r="W45" s="194"/>
+      <c r="X45" s="194"/>
+      <c r="Y45" s="194"/>
+      <c r="Z45" s="194"/>
     </row>
     <row r="46" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A46" s="174">
@@ -57339,13 +57339,13 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:13" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="197" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="193"/>
-      <c r="C3" s="193"/>
-      <c r="D3" s="193"/>
-      <c r="E3" s="193"/>
+      <c r="B3" s="198"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
       <c r="F3" s="58"/>
       <c r="G3" s="58"/>
       <c r="H3" s="57"/>

--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -29812,7 +29812,7 @@
       <c r="A39" s="174">
         <v>20</v>
       </c>
-      <c r="B39" s="168" t="s">
+      <c r="B39" s="189" t="s">
         <v>69</v>
       </c>
       <c r="C39" s="170"/>
@@ -29846,7 +29846,7 @@
       <c r="A40" s="174">
         <v>21</v>
       </c>
-      <c r="B40" s="168" t="s">
+      <c r="B40" s="189" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="170"/>

--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -248,12 +248,6 @@
   </si>
   <si>
     <t>Hiển thị tất cả các khách hàng mua hàng (với tổng số tiền) trong khoảng từ ngày, đến ngày</t>
-  </si>
-  <si>
-    <t>Hiển thị tất cả đơn hàng với tổng số tiền</t>
-  </si>
-  <si>
-    <t>Hiển thị tất cả các nhân viên bán hàng với tổng số tiền bán được</t>
   </si>
   <si>
     <t>Hiển thị tất cả các mặt hàng không bán được</t>
@@ -659,6 +653,12 @@
   </si>
   <si>
     <t>Hiển thị tất cả các mặt hàng có Giá bán sau khi đã tính giảm giá &lt;= 1000, Sử dụng aggregate</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả đơn hàng với tổng số tiền bán được của mỗi đơn</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả các nhân viên với tổng số tiền bán được</t>
   </si>
 </sst>
 </file>
@@ -1841,7 +1841,7 @@
     <row r="2" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="76" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
@@ -1952,7 +1952,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
@@ -1990,7 +1990,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D6" s="7">
         <v>50</v>
@@ -2023,10 +2023,10 @@
     <row r="7" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="79"/>
       <c r="B7" s="80" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D7" s="82"/>
       <c r="E7" s="81"/>
@@ -2062,7 +2062,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D8" s="7">
         <v>500</v>
@@ -2097,10 +2097,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="130" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C9" s="131" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D9" s="130"/>
       <c r="E9" s="131"/>
@@ -2108,10 +2108,10 @@
       <c r="G9" s="130"/>
       <c r="H9" s="130"/>
       <c r="I9" s="130" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J9" s="118" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="K9" s="118"/>
       <c r="L9" s="118"/>
@@ -2135,10 +2135,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="133" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D10" s="133"/>
       <c r="E10" s="134"/>
@@ -2169,10 +2169,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="133" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C11" s="134" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" s="133"/>
       <c r="E11" s="134"/>
@@ -2203,10 +2203,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="133" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" s="134" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D12" s="133"/>
       <c r="E12" s="134"/>
@@ -2237,10 +2237,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D13" s="133"/>
       <c r="E13" s="134"/>
@@ -2274,7 +2274,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D14" s="133"/>
       <c r="E14" s="134"/>
@@ -2305,10 +2305,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="133" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C15" s="134" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D15" s="133"/>
       <c r="E15" s="134"/>
@@ -2339,10 +2339,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="133" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C16" s="134" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D16" s="133"/>
       <c r="E16" s="134"/>
@@ -2373,10 +2373,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="133" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C17" s="134" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D17" s="133"/>
       <c r="E17" s="134"/>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="19" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="196" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B19" s="196"/>
       <c r="C19" s="196"/>
@@ -2514,7 +2514,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
@@ -2552,7 +2552,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D22" s="17">
         <v>100</v>
@@ -2588,7 +2588,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D23" s="17">
         <v>50</v>
@@ -2626,7 +2626,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D24" s="17">
         <v>50</v>
@@ -2661,10 +2661,10 @@
     <row r="25" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="79"/>
       <c r="B25" s="80" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D25" s="82"/>
       <c r="E25" s="81"/>
@@ -2700,7 +2700,7 @@
         <v>18</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D26" s="17">
         <v>500</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="28" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="196" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B28" s="196"/>
       <c r="C28" s="196"/>
@@ -2840,7 +2840,7 @@
         <v>9</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D30" s="24">
         <v>50</v>
@@ -2878,7 +2878,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D31" s="28">
         <v>50</v>
@@ -2914,7 +2914,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D32" s="28">
         <v>50</v>
@@ -2950,7 +2950,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33" s="28">
         <v>50</v>
@@ -2988,7 +2988,7 @@
         <v>18</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D34" s="28">
         <v>500</v>
@@ -3026,7 +3026,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D35" s="93">
         <v>50</v>
@@ -3059,10 +3059,10 @@
     <row r="36" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="79"/>
       <c r="B36" s="80" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D36" s="82"/>
       <c r="E36" s="81"/>
@@ -3131,10 +3131,10 @@
         <v>8</v>
       </c>
       <c r="B38" s="92" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D38" s="93"/>
       <c r="E38" s="94"/>
@@ -3165,10 +3165,10 @@
         <v>9</v>
       </c>
       <c r="B39" s="136" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C39" s="137" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D39" s="138"/>
       <c r="E39" s="139"/>
@@ -3199,10 +3199,10 @@
         <v>10</v>
       </c>
       <c r="B40" s="136" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C40" s="137" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D40" s="138"/>
       <c r="E40" s="139"/>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="42" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="199" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B42" s="200"/>
       <c r="C42" s="200"/>
@@ -3340,7 +3340,7 @@
         <v>9</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D44" s="32">
         <v>50</v>
@@ -3378,7 +3378,7 @@
         <v>19</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D45" s="36">
         <v>50</v>
@@ -3414,7 +3414,7 @@
         <v>20</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D46" s="36">
         <v>50</v>
@@ -3450,7 +3450,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D47" s="36">
         <v>50</v>
@@ -3488,7 +3488,7 @@
         <v>18</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D48" s="36">
         <v>500</v>
@@ -3526,7 +3526,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="96" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D49" s="97">
         <v>50</v>
@@ -3559,10 +3559,10 @@
     <row r="50" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="79"/>
       <c r="B50" s="80" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D50" s="82"/>
       <c r="E50" s="81"/>
@@ -3631,10 +3631,10 @@
         <v>8</v>
       </c>
       <c r="B52" s="92" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D52" s="93"/>
       <c r="E52" s="94"/>
@@ -3665,10 +3665,10 @@
         <v>9</v>
       </c>
       <c r="B53" s="136" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C53" s="137" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D53" s="138"/>
       <c r="E53" s="139"/>
@@ -3699,10 +3699,10 @@
         <v>10</v>
       </c>
       <c r="B54" s="136" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C54" s="137" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D54" s="138"/>
       <c r="E54" s="139"/>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="56" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="202" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -3840,7 +3840,7 @@
         <v>9</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D58" s="41"/>
       <c r="E58" s="42"/>
@@ -3878,7 +3878,7 @@
         <v>12</v>
       </c>
       <c r="C59" s="44" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D59" s="45">
         <v>50</v>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="43" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I61" s="43"/>
       <c r="J61" s="77"/>
@@ -4026,7 +4026,7 @@
         <v>28</v>
       </c>
       <c r="C63" s="182" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D63" s="183"/>
       <c r="E63" s="184"/>
@@ -4064,7 +4064,7 @@
         <v>31</v>
       </c>
       <c r="C64" s="182" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D64" s="183"/>
       <c r="E64" s="184"/>
@@ -4102,7 +4102,7 @@
         <v>14</v>
       </c>
       <c r="C65" s="81" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D65" s="82">
         <v>3000</v>
@@ -4135,10 +4135,10 @@
         <v>9</v>
       </c>
       <c r="B66" s="80" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C66" s="81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D66" s="82"/>
       <c r="E66" s="81"/>
@@ -4171,10 +4171,10 @@
         <v>10</v>
       </c>
       <c r="B67" s="99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C67" s="100" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D67" s="101"/>
       <c r="E67" s="100"/>
@@ -4182,7 +4182,7 @@
       <c r="G67" s="99"/>
       <c r="H67" s="102"/>
       <c r="I67" s="99" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J67" s="103"/>
       <c r="K67" s="103"/>
@@ -4207,10 +4207,10 @@
         <v>11</v>
       </c>
       <c r="B68" s="99" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C68" s="104" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D68" s="101"/>
       <c r="E68" s="100"/>
@@ -4241,10 +4241,10 @@
         <v>12</v>
       </c>
       <c r="B69" s="99" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C69" s="100" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D69" s="101"/>
       <c r="E69" s="100"/>
@@ -4252,7 +4252,7 @@
       <c r="G69" s="99"/>
       <c r="H69" s="102"/>
       <c r="I69" s="99" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J69" s="103"/>
       <c r="K69" s="103"/>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="71" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="203" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B71" s="204"/>
       <c r="C71" s="204"/>
@@ -4384,7 +4384,7 @@
         <v>9</v>
       </c>
       <c r="C73" s="142" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D73" s="143"/>
       <c r="E73" s="144"/>
@@ -4428,7 +4428,7 @@
       <c r="E74" s="148"/>
       <c r="F74" s="149"/>
       <c r="G74" s="145" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H74" s="145" t="s">
         <v>35</v>
@@ -4498,7 +4498,7 @@
         <v>37</v>
       </c>
       <c r="C76" s="146" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D76" s="150">
         <v>50</v>
@@ -4538,7 +4538,7 @@
         <v>14</v>
       </c>
       <c r="C77" s="146" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D77" s="150" t="s">
         <v>33</v>
@@ -4576,7 +4576,7 @@
         <v>40</v>
       </c>
       <c r="C78" s="146" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D78" s="150">
         <v>500</v>
@@ -4612,7 +4612,7 @@
         <v>41</v>
       </c>
       <c r="C79" s="146" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D79" s="150">
         <v>20</v>
@@ -4623,7 +4623,7 @@
         <v>42</v>
       </c>
       <c r="H79" s="145" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I79" s="145"/>
       <c r="J79" s="77"/>
@@ -4652,7 +4652,7 @@
         <v>43</v>
       </c>
       <c r="C80" s="146" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D80" s="150">
         <v>50</v>
@@ -4687,10 +4687,10 @@
     <row r="81" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="79"/>
       <c r="B81" s="80" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C81" s="81" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D81" s="82"/>
       <c r="E81" s="81"/>
@@ -4719,10 +4719,10 @@
     <row r="82" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="79"/>
       <c r="B82" s="80" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C82" s="81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D82" s="82"/>
       <c r="E82" s="81"/>
@@ -4755,10 +4755,10 @@
         <v>9</v>
       </c>
       <c r="B83" s="145" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C83" s="146" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D83" s="150">
         <v>50</v>
@@ -4800,7 +4800,7 @@
         <v>45</v>
       </c>
       <c r="C84" s="146" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D84" s="150">
         <v>50</v>
@@ -4839,10 +4839,10 @@
         <v>10</v>
       </c>
       <c r="B85" s="106" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C85" s="107" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D85" s="108"/>
       <c r="E85" s="109"/>
@@ -4887,10 +4887,10 @@
         <v>11</v>
       </c>
       <c r="B86" s="106" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C86" s="107" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D86" s="108"/>
       <c r="E86" s="109"/>
@@ -4935,10 +4935,10 @@
         <v>12</v>
       </c>
       <c r="B87" s="106" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C87" s="107" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D87" s="108"/>
       <c r="E87" s="109"/>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="89" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="205" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B89" s="204"/>
       <c r="C89" s="204"/>
@@ -5090,7 +5090,7 @@
         <v>9</v>
       </c>
       <c r="C91" s="154" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D91" s="155"/>
       <c r="E91" s="156"/>
@@ -5128,7 +5128,7 @@
         <v>47</v>
       </c>
       <c r="C92" s="159" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D92" s="160"/>
       <c r="E92" s="161"/>
@@ -5229,10 +5229,10 @@
     <row r="95" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="79"/>
       <c r="B95" s="80" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C95" s="81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D95" s="82"/>
       <c r="E95" s="81"/>
@@ -5268,7 +5268,7 @@
         <v>25</v>
       </c>
       <c r="C96" s="159" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D96" s="160"/>
       <c r="E96" s="161"/>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="98" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="203" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B98" s="204"/>
       <c r="C98" s="204"/>
@@ -5406,7 +5406,7 @@
         <v>9</v>
       </c>
       <c r="C100" s="142" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D100" s="143"/>
       <c r="E100" s="144"/>
@@ -5439,10 +5439,10 @@
     <row r="101" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="79"/>
       <c r="B101" s="80" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C101" s="81" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D101" s="82"/>
       <c r="E101" s="81"/>
@@ -5476,7 +5476,7 @@
         <v>43</v>
       </c>
       <c r="C102" s="146" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D102" s="150">
         <v>50</v>
@@ -5538,7 +5538,7 @@
     </row>
     <row r="104" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="205" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B104" s="204"/>
       <c r="C104" s="204"/>
@@ -5620,7 +5620,7 @@
         <v>9</v>
       </c>
       <c r="C106" s="154" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D106" s="155"/>
       <c r="E106" s="156"/>
@@ -5658,7 +5658,7 @@
         <v>47</v>
       </c>
       <c r="C107" s="159" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D107" s="160"/>
       <c r="E107" s="161"/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="158" spans="1:36" s="78" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A158" s="197" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B158" s="198"/>
       <c r="C158" s="198"/>
@@ -6414,7 +6414,7 @@
         <v>9</v>
       </c>
       <c r="C160" s="113" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D160" s="114"/>
       <c r="E160" s="115"/>
@@ -6459,10 +6459,10 @@
         <v>2</v>
       </c>
       <c r="B161" s="119" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C161" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D161" s="121"/>
       <c r="E161" s="122"/>
@@ -6503,14 +6503,14 @@
         <v>3</v>
       </c>
       <c r="B162" s="119" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C162" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D162" s="121"/>
       <c r="E162" s="122" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F162" s="119"/>
       <c r="G162" s="119"/>
@@ -6549,10 +6549,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="119" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C163" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D163" s="121"/>
       <c r="E163" s="122"/>
@@ -6593,10 +6593,10 @@
         <v>5</v>
       </c>
       <c r="B164" s="119" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C164" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D164" s="121"/>
       <c r="E164" s="122"/>
@@ -6637,10 +6637,10 @@
         <v>6</v>
       </c>
       <c r="B165" s="119" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C165" s="120" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D165" s="121"/>
       <c r="E165" s="122"/>
@@ -6648,7 +6648,7 @@
       <c r="G165" s="119"/>
       <c r="H165" s="123"/>
       <c r="I165" s="119" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J165" s="77"/>
       <c r="K165" s="77"/>
@@ -6683,10 +6683,10 @@
         <v>7</v>
       </c>
       <c r="B166" s="119" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C166" s="120" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D166" s="121"/>
       <c r="E166" s="122"/>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="168" spans="1:36" s="78" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="197" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B168" s="198"/>
       <c r="C168" s="198"/>
@@ -6864,7 +6864,7 @@
         <v>9</v>
       </c>
       <c r="C170" s="125" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D170" s="126"/>
       <c r="E170" s="127"/>
@@ -6909,10 +6909,10 @@
         <v>2</v>
       </c>
       <c r="B171" s="119" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C171" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D171" s="121"/>
       <c r="E171" s="122"/>
@@ -6953,14 +6953,14 @@
         <v>3</v>
       </c>
       <c r="B172" s="119" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C172" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D172" s="121"/>
       <c r="E172" s="122" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F172" s="119"/>
       <c r="G172" s="119"/>
@@ -6999,10 +6999,10 @@
         <v>4</v>
       </c>
       <c r="B173" s="119" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C173" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D173" s="121"/>
       <c r="E173" s="122"/>
@@ -7043,10 +7043,10 @@
         <v>5</v>
       </c>
       <c r="B174" s="119" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C174" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D174" s="121"/>
       <c r="E174" s="122"/>
@@ -7087,10 +7087,10 @@
         <v>6</v>
       </c>
       <c r="B175" s="119" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C175" s="120" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D175" s="121"/>
       <c r="E175" s="122"/>
@@ -7098,7 +7098,7 @@
       <c r="G175" s="119"/>
       <c r="H175" s="123"/>
       <c r="I175" s="119" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J175" s="77"/>
       <c r="K175" s="77"/>
@@ -7133,10 +7133,10 @@
         <v>7</v>
       </c>
       <c r="B176" s="119" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C176" s="120" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D176" s="121"/>
       <c r="E176" s="122"/>
@@ -7180,13 +7180,13 @@
         <v>34</v>
       </c>
       <c r="C177" s="120" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D177" s="121"/>
       <c r="E177" s="122"/>
       <c r="F177" s="119"/>
       <c r="G177" s="119" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H177" s="123"/>
       <c r="I177" s="119"/>
@@ -7221,10 +7221,10 @@
     <row r="178" spans="1:36" s="105" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A178" s="119"/>
       <c r="B178" s="119" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C178" s="120" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D178" s="121"/>
       <c r="E178" s="122"/>
@@ -7263,10 +7263,10 @@
     <row r="179" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="119"/>
       <c r="B179" s="119" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C179" s="120" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D179" s="121"/>
       <c r="E179" s="122"/>
@@ -7305,10 +7305,10 @@
     <row r="180" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="119"/>
       <c r="B180" s="119" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C180" s="120" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D180" s="121"/>
       <c r="E180" s="122"/>
@@ -7347,10 +7347,10 @@
     <row r="181" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="119"/>
       <c r="B181" s="119" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C181" s="120" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D181" s="121"/>
       <c r="E181" s="122"/>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="183" spans="1:36" s="78" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="197" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B183" s="198"/>
       <c r="C183" s="198"/>
@@ -7528,7 +7528,7 @@
         <v>9</v>
       </c>
       <c r="C185" s="125" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D185" s="126"/>
       <c r="E185" s="127"/>
@@ -7576,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C186" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D186" s="121"/>
       <c r="E186" s="122"/>
@@ -7619,10 +7619,10 @@
         <v>3</v>
       </c>
       <c r="B187" s="119" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C187" s="120" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D187" s="121"/>
       <c r="E187" s="122"/>
@@ -7663,10 +7663,10 @@
         <v>4</v>
       </c>
       <c r="B188" s="119" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C188" s="120" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D188" s="121"/>
       <c r="E188" s="122"/>
@@ -7707,10 +7707,10 @@
         <v>5</v>
       </c>
       <c r="B189" s="119" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C189" s="120" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D189" s="121"/>
       <c r="E189" s="122"/>
@@ -7751,10 +7751,10 @@
         <v>6</v>
       </c>
       <c r="B190" s="119" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C190" s="120" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D190" s="121"/>
       <c r="E190" s="122"/>
@@ -28529,16 +28529,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="162" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C1" s="169" t="s">
         <v>37</v>
       </c>
       <c r="D1" s="169" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E1" s="169" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F1" s="55"/>
       <c r="G1" s="55"/>
@@ -28567,7 +28567,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="163" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C2" s="170"/>
       <c r="D2" s="170"/>
@@ -28599,7 +28599,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="163" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3" s="170"/>
       <c r="D3" s="170"/>
@@ -28631,7 +28631,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="163" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="170"/>
       <c r="D4" s="170"/>
@@ -28663,7 +28663,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="163" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C5" s="170"/>
       <c r="D5" s="170"/>
@@ -28695,7 +28695,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="163" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" s="170"/>
       <c r="D6" s="170"/>
@@ -28727,7 +28727,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="170"/>
       <c r="D7" s="170"/>
@@ -28795,7 +28795,7 @@
       </c>
       <c r="C9" s="170"/>
       <c r="D9" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" s="170"/>
       <c r="F9" s="54"/>
@@ -28822,14 +28822,14 @@
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="85" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B10" s="164" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C10" s="170"/>
       <c r="D10" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E10" s="170"/>
       <c r="F10" s="54"/>
@@ -28856,14 +28856,14 @@
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="85" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B11" s="164" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C11" s="170"/>
       <c r="D11" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E11" s="170"/>
       <c r="F11" s="54"/>
@@ -28893,11 +28893,11 @@
         <v>2</v>
       </c>
       <c r="B12" s="164" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C12" s="170"/>
       <c r="D12" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E12" s="170"/>
       <c r="F12" s="54"/>
@@ -28924,14 +28924,14 @@
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="85" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B13" s="164" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C13" s="170"/>
       <c r="D13" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E13" s="170"/>
       <c r="F13" s="54"/>
@@ -28958,14 +28958,14 @@
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="85" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B14" s="164" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E14" s="170"/>
       <c r="F14" s="54"/>
@@ -28995,11 +28995,11 @@
         <v>3</v>
       </c>
       <c r="B15" s="164" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C15" s="170"/>
       <c r="D15" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E15" s="170"/>
       <c r="F15" s="54"/>
@@ -29026,14 +29026,14 @@
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="85" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B16" s="164" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C16" s="170"/>
       <c r="D16" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E16" s="170"/>
       <c r="F16" s="54"/>
@@ -29060,14 +29060,14 @@
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="85" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B17" s="164" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C17" s="170"/>
       <c r="D17" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E17" s="170"/>
       <c r="F17" s="54"/>
@@ -29094,14 +29094,14 @@
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="85" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B18" s="164" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C18" s="170"/>
       <c r="D18" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E18" s="170"/>
       <c r="F18" s="54"/>
@@ -29128,14 +29128,14 @@
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="85" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B19" s="164" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C19" s="170"/>
       <c r="D19" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E19" s="170"/>
       <c r="F19" s="54"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="C20" s="170"/>
       <c r="D20" s="170" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E20" s="170"/>
       <c r="F20" s="54"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="C21" s="170"/>
       <c r="D21" s="170" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E21" s="170"/>
       <c r="F21" s="54"/>
@@ -29230,14 +29230,14 @@
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="173" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B22" s="165" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C22" s="170"/>
       <c r="D22" s="170" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E22" s="170"/>
       <c r="F22" s="54"/>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C23" s="170"/>
       <c r="D23" s="170" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E23" s="170"/>
       <c r="F23" s="54"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="C24" s="170"/>
       <c r="D24" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24" s="170"/>
       <c r="F24" s="54"/>
@@ -29332,14 +29332,14 @@
     </row>
     <row r="25" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A25" s="75" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B25" s="166" t="s">
         <v>58</v>
       </c>
       <c r="C25" s="170"/>
       <c r="D25" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E25" s="170"/>
       <c r="F25" s="54"/>
@@ -29366,14 +29366,14 @@
     </row>
     <row r="26" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A26" s="75" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B26" s="166" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C26" s="170"/>
       <c r="D26" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E26" s="170"/>
       <c r="F26" s="54"/>
@@ -29400,14 +29400,14 @@
     </row>
     <row r="27" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A27" s="75" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B27" s="166" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C27" s="170"/>
       <c r="D27" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E27" s="170"/>
       <c r="F27" s="54"/>
@@ -29441,7 +29441,7 @@
       </c>
       <c r="C28" s="170"/>
       <c r="D28" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E28" s="170"/>
       <c r="F28" s="54"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="C29" s="170"/>
       <c r="D29" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E29" s="170"/>
       <c r="F29" s="54"/>
@@ -29509,7 +29509,7 @@
       </c>
       <c r="C30" s="170"/>
       <c r="D30" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E30" s="170"/>
       <c r="F30" s="54"/>
@@ -29543,7 +29543,7 @@
       </c>
       <c r="C31" s="170"/>
       <c r="D31" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E31" s="170"/>
       <c r="F31" s="54"/>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="C32" s="170"/>
       <c r="D32" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E32" s="170"/>
       <c r="F32" s="54"/>
@@ -29611,7 +29611,7 @@
       </c>
       <c r="C33" s="170"/>
       <c r="D33" s="170" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E33" s="170"/>
       <c r="F33" s="54"/>
@@ -29641,14 +29641,14 @@
         <v>15</v>
       </c>
       <c r="B34" s="168" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C34" s="170"/>
       <c r="D34" s="170" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E34" s="170" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F34" s="54"/>
       <c r="G34" s="54"/>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="C35" s="170"/>
       <c r="D35" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E35" s="170"/>
       <c r="F35" s="54"/>
@@ -29715,7 +29715,7 @@
       </c>
       <c r="C36" s="170"/>
       <c r="D36" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E36" s="170"/>
       <c r="F36" s="54"/>
@@ -29749,7 +29749,7 @@
       </c>
       <c r="C37" s="190"/>
       <c r="D37" s="190" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E37" s="190"/>
       <c r="F37" s="111"/>
@@ -29783,7 +29783,7 @@
       </c>
       <c r="C38" s="170"/>
       <c r="D38" s="170" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E38" s="170"/>
       <c r="F38" s="54"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="C39" s="170"/>
       <c r="D39" s="170" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E39" s="170"/>
       <c r="F39" s="54"/>
@@ -29911,7 +29911,7 @@
         <v>23</v>
       </c>
       <c r="B42" s="168" t="s">
-        <v>72</v>
+        <v>207</v>
       </c>
       <c r="C42" s="170"/>
       <c r="D42" s="170"/>
@@ -29942,8 +29942,8 @@
       <c r="A43" s="174">
         <v>24</v>
       </c>
-      <c r="B43" s="168" t="s">
-        <v>73</v>
+      <c r="B43" s="189" t="s">
+        <v>208</v>
       </c>
       <c r="C43" s="170"/>
       <c r="D43" s="170"/>
@@ -29975,11 +29975,11 @@
         <v>25</v>
       </c>
       <c r="B44" s="168" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C44" s="170"/>
       <c r="D44" s="170" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E44" s="170"/>
       <c r="F44" s="54"/>
@@ -30009,11 +30009,11 @@
         <v>26</v>
       </c>
       <c r="B45" s="192" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C45" s="193"/>
       <c r="D45" s="193" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E45" s="193"/>
       <c r="F45" s="194"/>
@@ -30043,12 +30043,12 @@
         <v>27</v>
       </c>
       <c r="B46" s="168" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C46" s="170"/>
       <c r="D46" s="170"/>
       <c r="E46" s="170" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F46" s="54"/>
       <c r="G46" s="54"/>
@@ -30077,7 +30077,7 @@
         <v>28</v>
       </c>
       <c r="B47" s="168" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C47" s="170"/>
       <c r="D47" s="170"/>
@@ -30109,12 +30109,12 @@
         <v>29</v>
       </c>
       <c r="B48" s="168" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C48" s="170"/>
       <c r="D48" s="170"/>
       <c r="E48" s="170" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F48" s="54"/>
       <c r="G48" s="54"/>
@@ -30143,12 +30143,12 @@
         <v>30</v>
       </c>
       <c r="B49" s="168" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C49" s="170"/>
       <c r="D49" s="170"/>
       <c r="E49" s="170" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F49" s="54"/>
       <c r="G49" s="54"/>
@@ -30177,7 +30177,7 @@
         <v>31</v>
       </c>
       <c r="B50" s="168" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C50" s="170"/>
       <c r="D50" s="170"/>
@@ -30209,7 +30209,7 @@
         <v>32</v>
       </c>
       <c r="B51" s="168" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C51" s="170"/>
       <c r="D51" s="170"/>
@@ -30241,7 +30241,7 @@
         <v>33</v>
       </c>
       <c r="B52" s="168" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C52" s="170"/>
       <c r="D52" s="170"/>
@@ -30273,7 +30273,7 @@
         <v>34</v>
       </c>
       <c r="B53" s="168" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C53" s="170"/>
       <c r="D53" s="170"/>
@@ -57340,7 +57340,7 @@
   <sheetData>
     <row r="3" spans="1:13" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A3" s="197" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B3" s="198"/>
       <c r="C3" s="198"/>
@@ -57388,7 +57388,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" s="63"/>
       <c r="E5" s="64"/>
@@ -57409,7 +57409,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D6" s="69"/>
       <c r="E6" s="70"/>
@@ -57425,10 +57425,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="68" t="s">
         <v>139</v>
-      </c>
-      <c r="C7" s="68" t="s">
-        <v>141</v>
       </c>
       <c r="D7" s="69"/>
       <c r="E7" s="70"/>
@@ -57437,7 +57437,7 @@
       <c r="H7" s="71"/>
       <c r="I7" s="67"/>
       <c r="L7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.45" x14ac:dyDescent="0.4">
@@ -57445,10 +57445,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D8" s="69"/>
       <c r="E8" s="70"/>
@@ -57462,10 +57462,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D9" s="69"/>
       <c r="E9" s="70"/>
@@ -57473,10 +57473,10 @@
       <c r="G9" s="67"/>
       <c r="H9" s="71"/>
       <c r="I9" s="67" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L9" s="73" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M9" s="74"/>
     </row>
@@ -57490,10 +57490,10 @@
       <c r="G10" s="67"/>
       <c r="H10" s="71"/>
       <c r="I10" s="67" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L10" s="73" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M10" s="74"/>
     </row>
@@ -57520,36 +57520,36 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="L14" s="73" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M14" s="74" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" t="s">
         <v>149</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>150</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>151</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>152</v>
       </c>
-      <c r="H15" t="s">
+      <c r="J15" t="s">
         <v>153</v>
       </c>
-      <c r="I15" t="s">
-        <v>154</v>
-      </c>
-      <c r="J15" t="s">
-        <v>155</v>
-      </c>
       <c r="L15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M15">
         <v>15</v>
@@ -57557,117 +57557,117 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="D16" s="73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E16" s="73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F16" s="73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G16" s="73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H16" s="73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I16" s="73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="J16" s="73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="H17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D18" s="73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E18" s="73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F18" s="73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G18" s="73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H18" s="73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I18" s="73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J18" s="73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="I19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D20" s="73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E20" s="73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F20" s="73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G20" s="73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H20" s="73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I20" s="73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J20" s="73" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -29744,7 +29744,7 @@
       <c r="A37" s="188">
         <v>18</v>
       </c>
-      <c r="B37" s="189" t="s">
+      <c r="B37" s="168" t="s">
         <v>67</v>
       </c>
       <c r="C37" s="190"/>
@@ -29812,7 +29812,7 @@
       <c r="A39" s="174">
         <v>20</v>
       </c>
-      <c r="B39" s="189" t="s">
+      <c r="B39" s="168" t="s">
         <v>69</v>
       </c>
       <c r="C39" s="170"/>
@@ -29846,7 +29846,7 @@
       <c r="A40" s="174">
         <v>21</v>
       </c>
-      <c r="B40" s="189" t="s">
+      <c r="B40" s="168" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="170"/>
@@ -29942,7 +29942,7 @@
       <c r="A43" s="174">
         <v>24</v>
       </c>
-      <c r="B43" s="189" t="s">
+      <c r="B43" s="168" t="s">
         <v>208</v>
       </c>
       <c r="C43" s="170"/>
@@ -29974,7 +29974,7 @@
       <c r="A44" s="174">
         <v>25</v>
       </c>
-      <c r="B44" s="168" t="s">
+      <c r="B44" s="189" t="s">
         <v>72</v>
       </c>
       <c r="C44" s="170"/>

--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -260,9 +260,6 @@
   </si>
   <si>
     <t>Hiển thị top 5 các khách hàng mua hàng với tổng số tiền mua được từ cao đến thấp trong khoảng từ ngày, đến ngày</t>
-  </si>
-  <si>
-    <t>Hiển thị danh sách các mức giảm giá của cửa hàng</t>
   </si>
   <si>
     <t>Hiển thị tất cả danh mục (Categories) với tổng số tiền bán được trong mỗi danh mục</t>
@@ -659,6 +656,9 @@
   </si>
   <si>
     <t>Hiển thị tất cả các nhân viên với tổng số tiền bán được</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách các mức giảm giá của sản phẩm</t>
   </si>
 </sst>
 </file>
@@ -1841,7 +1841,7 @@
     <row r="2" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="76" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1870,7 +1870,7 @@
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
@@ -1952,7 +1952,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
@@ -1990,7 +1990,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D6" s="7">
         <v>50</v>
@@ -2023,10 +2023,10 @@
     <row r="7" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="79"/>
       <c r="B7" s="80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D7" s="82"/>
       <c r="E7" s="81"/>
@@ -2062,7 +2062,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D8" s="7">
         <v>500</v>
@@ -2097,10 +2097,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="130" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="131" t="s">
         <v>118</v>
-      </c>
-      <c r="C9" s="131" t="s">
-        <v>119</v>
       </c>
       <c r="D9" s="130"/>
       <c r="E9" s="131"/>
@@ -2108,10 +2108,10 @@
       <c r="G9" s="130"/>
       <c r="H9" s="130"/>
       <c r="I9" s="130" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J9" s="118" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K9" s="118"/>
       <c r="L9" s="118"/>
@@ -2135,10 +2135,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="133" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D10" s="133"/>
       <c r="E10" s="134"/>
@@ -2169,10 +2169,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="133" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="134" t="s">
         <v>113</v>
-      </c>
-      <c r="C11" s="134" t="s">
-        <v>114</v>
       </c>
       <c r="D11" s="133"/>
       <c r="E11" s="134"/>
@@ -2203,10 +2203,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="133" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="134" t="s">
         <v>116</v>
-      </c>
-      <c r="C12" s="134" t="s">
-        <v>117</v>
       </c>
       <c r="D12" s="133"/>
       <c r="E12" s="134"/>
@@ -2237,10 +2237,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" s="133"/>
       <c r="E13" s="134"/>
@@ -2274,7 +2274,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D14" s="133"/>
       <c r="E14" s="134"/>
@@ -2305,10 +2305,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="133" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C15" s="134" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" s="133"/>
       <c r="E15" s="134"/>
@@ -2339,10 +2339,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C16" s="134" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D16" s="133"/>
       <c r="E16" s="134"/>
@@ -2373,10 +2373,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="133" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C17" s="134" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D17" s="133"/>
       <c r="E17" s="134"/>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="19" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="196" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B19" s="196"/>
       <c r="C19" s="196"/>
@@ -2514,7 +2514,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
@@ -2552,7 +2552,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D22" s="17">
         <v>100</v>
@@ -2588,7 +2588,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" s="17">
         <v>50</v>
@@ -2626,7 +2626,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D24" s="17">
         <v>50</v>
@@ -2661,10 +2661,10 @@
     <row r="25" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="79"/>
       <c r="B25" s="80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D25" s="82"/>
       <c r="E25" s="81"/>
@@ -2700,7 +2700,7 @@
         <v>18</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="17">
         <v>500</v>
@@ -2758,7 +2758,7 @@
     </row>
     <row r="28" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="196" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B28" s="196"/>
       <c r="C28" s="196"/>
@@ -2840,7 +2840,7 @@
         <v>9</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D30" s="24">
         <v>50</v>
@@ -2878,7 +2878,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D31" s="28">
         <v>50</v>
@@ -2914,7 +2914,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" s="28">
         <v>50</v>
@@ -2950,7 +2950,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="28">
         <v>50</v>
@@ -2988,7 +2988,7 @@
         <v>18</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D34" s="28">
         <v>500</v>
@@ -3026,7 +3026,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D35" s="93">
         <v>50</v>
@@ -3059,10 +3059,10 @@
     <row r="36" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="79"/>
       <c r="B36" s="80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D36" s="82"/>
       <c r="E36" s="81"/>
@@ -3131,10 +3131,10 @@
         <v>8</v>
       </c>
       <c r="B38" s="92" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D38" s="93"/>
       <c r="E38" s="94"/>
@@ -3165,10 +3165,10 @@
         <v>9</v>
       </c>
       <c r="B39" s="136" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="137" t="s">
         <v>132</v>
-      </c>
-      <c r="C39" s="137" t="s">
-        <v>133</v>
       </c>
       <c r="D39" s="138"/>
       <c r="E39" s="139"/>
@@ -3199,10 +3199,10 @@
         <v>10</v>
       </c>
       <c r="B40" s="136" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="137" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D40" s="138"/>
       <c r="E40" s="139"/>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="42" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="199" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B42" s="200"/>
       <c r="C42" s="200"/>
@@ -3340,7 +3340,7 @@
         <v>9</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D44" s="32">
         <v>50</v>
@@ -3378,7 +3378,7 @@
         <v>19</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D45" s="36">
         <v>50</v>
@@ -3414,7 +3414,7 @@
         <v>20</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D46" s="36">
         <v>50</v>
@@ -3450,7 +3450,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D47" s="36">
         <v>50</v>
@@ -3488,7 +3488,7 @@
         <v>18</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D48" s="36">
         <v>500</v>
@@ -3526,7 +3526,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="96" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D49" s="97">
         <v>50</v>
@@ -3559,10 +3559,10 @@
     <row r="50" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="79"/>
       <c r="B50" s="80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D50" s="82"/>
       <c r="E50" s="81"/>
@@ -3631,10 +3631,10 @@
         <v>8</v>
       </c>
       <c r="B52" s="92" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D52" s="93"/>
       <c r="E52" s="94"/>
@@ -3665,10 +3665,10 @@
         <v>9</v>
       </c>
       <c r="B53" s="136" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>132</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>133</v>
       </c>
       <c r="D53" s="138"/>
       <c r="E53" s="139"/>
@@ -3699,10 +3699,10 @@
         <v>10</v>
       </c>
       <c r="B54" s="136" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C54" s="137" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D54" s="138"/>
       <c r="E54" s="139"/>
@@ -3758,7 +3758,7 @@
     </row>
     <row r="56" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="202" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -3840,7 +3840,7 @@
         <v>9</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D58" s="41"/>
       <c r="E58" s="42"/>
@@ -3878,7 +3878,7 @@
         <v>12</v>
       </c>
       <c r="C59" s="44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D59" s="45">
         <v>50</v>
@@ -3961,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I61" s="43"/>
       <c r="J61" s="77"/>
@@ -4026,7 +4026,7 @@
         <v>28</v>
       </c>
       <c r="C63" s="182" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D63" s="183"/>
       <c r="E63" s="184"/>
@@ -4064,7 +4064,7 @@
         <v>31</v>
       </c>
       <c r="C64" s="182" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D64" s="183"/>
       <c r="E64" s="184"/>
@@ -4102,7 +4102,7 @@
         <v>14</v>
       </c>
       <c r="C65" s="81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D65" s="82">
         <v>3000</v>
@@ -4135,10 +4135,10 @@
         <v>9</v>
       </c>
       <c r="B66" s="80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C66" s="81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D66" s="82"/>
       <c r="E66" s="81"/>
@@ -4171,10 +4171,10 @@
         <v>10</v>
       </c>
       <c r="B67" s="99" t="s">
+        <v>117</v>
+      </c>
+      <c r="C67" s="100" t="s">
         <v>118</v>
-      </c>
-      <c r="C67" s="100" t="s">
-        <v>119</v>
       </c>
       <c r="D67" s="101"/>
       <c r="E67" s="100"/>
@@ -4182,7 +4182,7 @@
       <c r="G67" s="99"/>
       <c r="H67" s="102"/>
       <c r="I67" s="99" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J67" s="103"/>
       <c r="K67" s="103"/>
@@ -4207,10 +4207,10 @@
         <v>11</v>
       </c>
       <c r="B68" s="99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C68" s="104" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68" s="101"/>
       <c r="E68" s="100"/>
@@ -4241,10 +4241,10 @@
         <v>12</v>
       </c>
       <c r="B69" s="99" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="100" t="s">
         <v>126</v>
-      </c>
-      <c r="C69" s="100" t="s">
-        <v>127</v>
       </c>
       <c r="D69" s="101"/>
       <c r="E69" s="100"/>
@@ -4252,7 +4252,7 @@
       <c r="G69" s="99"/>
       <c r="H69" s="102"/>
       <c r="I69" s="99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J69" s="103"/>
       <c r="K69" s="103"/>
@@ -4302,7 +4302,7 @@
     </row>
     <row r="71" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="203" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B71" s="204"/>
       <c r="C71" s="204"/>
@@ -4384,7 +4384,7 @@
         <v>9</v>
       </c>
       <c r="C73" s="142" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D73" s="143"/>
       <c r="E73" s="144"/>
@@ -4428,7 +4428,7 @@
       <c r="E74" s="148"/>
       <c r="F74" s="149"/>
       <c r="G74" s="145" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H74" s="145" t="s">
         <v>35</v>
@@ -4498,7 +4498,7 @@
         <v>37</v>
       </c>
       <c r="C76" s="146" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D76" s="150">
         <v>50</v>
@@ -4538,7 +4538,7 @@
         <v>14</v>
       </c>
       <c r="C77" s="146" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D77" s="150" t="s">
         <v>33</v>
@@ -4576,7 +4576,7 @@
         <v>40</v>
       </c>
       <c r="C78" s="146" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D78" s="150">
         <v>500</v>
@@ -4612,7 +4612,7 @@
         <v>41</v>
       </c>
       <c r="C79" s="146" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D79" s="150">
         <v>20</v>
@@ -4623,7 +4623,7 @@
         <v>42</v>
       </c>
       <c r="H79" s="145" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I79" s="145"/>
       <c r="J79" s="77"/>
@@ -4652,7 +4652,7 @@
         <v>43</v>
       </c>
       <c r="C80" s="146" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D80" s="150">
         <v>50</v>
@@ -4687,10 +4687,10 @@
     <row r="81" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="79"/>
       <c r="B81" s="80" t="s">
+        <v>185</v>
+      </c>
+      <c r="C81" s="81" t="s">
         <v>186</v>
-      </c>
-      <c r="C81" s="81" t="s">
-        <v>187</v>
       </c>
       <c r="D81" s="82"/>
       <c r="E81" s="81"/>
@@ -4719,10 +4719,10 @@
     <row r="82" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="79"/>
       <c r="B82" s="80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C82" s="81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D82" s="82"/>
       <c r="E82" s="81"/>
@@ -4755,10 +4755,10 @@
         <v>9</v>
       </c>
       <c r="B83" s="145" t="s">
+        <v>188</v>
+      </c>
+      <c r="C83" s="146" t="s">
         <v>189</v>
-      </c>
-      <c r="C83" s="146" t="s">
-        <v>190</v>
       </c>
       <c r="D83" s="150">
         <v>50</v>
@@ -4800,7 +4800,7 @@
         <v>45</v>
       </c>
       <c r="C84" s="146" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D84" s="150">
         <v>50</v>
@@ -4839,10 +4839,10 @@
         <v>10</v>
       </c>
       <c r="B85" s="106" t="s">
+        <v>120</v>
+      </c>
+      <c r="C85" s="107" t="s">
         <v>121</v>
-      </c>
-      <c r="C85" s="107" t="s">
-        <v>122</v>
       </c>
       <c r="D85" s="108"/>
       <c r="E85" s="109"/>
@@ -4887,10 +4887,10 @@
         <v>11</v>
       </c>
       <c r="B86" s="106" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C86" s="107" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D86" s="108"/>
       <c r="E86" s="109"/>
@@ -4935,10 +4935,10 @@
         <v>12</v>
       </c>
       <c r="B87" s="106" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C87" s="107" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D87" s="108"/>
       <c r="E87" s="109"/>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="89" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="205" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B89" s="204"/>
       <c r="C89" s="204"/>
@@ -5090,7 +5090,7 @@
         <v>9</v>
       </c>
       <c r="C91" s="154" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D91" s="155"/>
       <c r="E91" s="156"/>
@@ -5128,7 +5128,7 @@
         <v>47</v>
       </c>
       <c r="C92" s="159" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D92" s="160"/>
       <c r="E92" s="161"/>
@@ -5229,10 +5229,10 @@
     <row r="95" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="79"/>
       <c r="B95" s="80" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C95" s="81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D95" s="82"/>
       <c r="E95" s="81"/>
@@ -5268,7 +5268,7 @@
         <v>25</v>
       </c>
       <c r="C96" s="159" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D96" s="160"/>
       <c r="E96" s="161"/>
@@ -5324,7 +5324,7 @@
     </row>
     <row r="98" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="203" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B98" s="204"/>
       <c r="C98" s="204"/>
@@ -5406,7 +5406,7 @@
         <v>9</v>
       </c>
       <c r="C100" s="142" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D100" s="143"/>
       <c r="E100" s="144"/>
@@ -5439,10 +5439,10 @@
     <row r="101" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="79"/>
       <c r="B101" s="80" t="s">
+        <v>185</v>
+      </c>
+      <c r="C101" s="81" t="s">
         <v>186</v>
-      </c>
-      <c r="C101" s="81" t="s">
-        <v>187</v>
       </c>
       <c r="D101" s="82"/>
       <c r="E101" s="81"/>
@@ -5476,7 +5476,7 @@
         <v>43</v>
       </c>
       <c r="C102" s="146" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D102" s="150">
         <v>50</v>
@@ -5538,7 +5538,7 @@
     </row>
     <row r="104" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="205" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B104" s="204"/>
       <c r="C104" s="204"/>
@@ -5620,7 +5620,7 @@
         <v>9</v>
       </c>
       <c r="C106" s="154" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D106" s="155"/>
       <c r="E106" s="156"/>
@@ -5658,7 +5658,7 @@
         <v>47</v>
       </c>
       <c r="C107" s="159" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D107" s="160"/>
       <c r="E107" s="161"/>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="158" spans="1:36" s="78" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A158" s="197" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B158" s="198"/>
       <c r="C158" s="198"/>
@@ -6414,7 +6414,7 @@
         <v>9</v>
       </c>
       <c r="C160" s="113" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D160" s="114"/>
       <c r="E160" s="115"/>
@@ -6459,10 +6459,10 @@
         <v>2</v>
       </c>
       <c r="B161" s="119" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C161" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D161" s="121"/>
       <c r="E161" s="122"/>
@@ -6503,14 +6503,14 @@
         <v>3</v>
       </c>
       <c r="B162" s="119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C162" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D162" s="121"/>
       <c r="E162" s="122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F162" s="119"/>
       <c r="G162" s="119"/>
@@ -6549,10 +6549,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="119" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C163" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D163" s="121"/>
       <c r="E163" s="122"/>
@@ -6593,10 +6593,10 @@
         <v>5</v>
       </c>
       <c r="B164" s="119" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C164" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D164" s="121"/>
       <c r="E164" s="122"/>
@@ -6637,10 +6637,10 @@
         <v>6</v>
       </c>
       <c r="B165" s="119" t="s">
+        <v>112</v>
+      </c>
+      <c r="C165" s="120" t="s">
         <v>113</v>
-      </c>
-      <c r="C165" s="120" t="s">
-        <v>114</v>
       </c>
       <c r="D165" s="121"/>
       <c r="E165" s="122"/>
@@ -6648,7 +6648,7 @@
       <c r="G165" s="119"/>
       <c r="H165" s="123"/>
       <c r="I165" s="119" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J165" s="77"/>
       <c r="K165" s="77"/>
@@ -6683,10 +6683,10 @@
         <v>7</v>
       </c>
       <c r="B166" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="C166" s="120" t="s">
         <v>116</v>
-      </c>
-      <c r="C166" s="120" t="s">
-        <v>117</v>
       </c>
       <c r="D166" s="121"/>
       <c r="E166" s="122"/>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="168" spans="1:36" s="78" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="197" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B168" s="198"/>
       <c r="C168" s="198"/>
@@ -6864,7 +6864,7 @@
         <v>9</v>
       </c>
       <c r="C170" s="125" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D170" s="126"/>
       <c r="E170" s="127"/>
@@ -6909,10 +6909,10 @@
         <v>2</v>
       </c>
       <c r="B171" s="119" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C171" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D171" s="121"/>
       <c r="E171" s="122"/>
@@ -6953,14 +6953,14 @@
         <v>3</v>
       </c>
       <c r="B172" s="119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C172" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D172" s="121"/>
       <c r="E172" s="122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F172" s="119"/>
       <c r="G172" s="119"/>
@@ -6999,10 +6999,10 @@
         <v>4</v>
       </c>
       <c r="B173" s="119" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C173" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D173" s="121"/>
       <c r="E173" s="122"/>
@@ -7043,10 +7043,10 @@
         <v>5</v>
       </c>
       <c r="B174" s="119" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C174" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D174" s="121"/>
       <c r="E174" s="122"/>
@@ -7087,10 +7087,10 @@
         <v>6</v>
       </c>
       <c r="B175" s="119" t="s">
+        <v>112</v>
+      </c>
+      <c r="C175" s="120" t="s">
         <v>113</v>
-      </c>
-      <c r="C175" s="120" t="s">
-        <v>114</v>
       </c>
       <c r="D175" s="121"/>
       <c r="E175" s="122"/>
@@ -7098,7 +7098,7 @@
       <c r="G175" s="119"/>
       <c r="H175" s="123"/>
       <c r="I175" s="119" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J175" s="77"/>
       <c r="K175" s="77"/>
@@ -7133,10 +7133,10 @@
         <v>7</v>
       </c>
       <c r="B176" s="119" t="s">
+        <v>115</v>
+      </c>
+      <c r="C176" s="120" t="s">
         <v>116</v>
-      </c>
-      <c r="C176" s="120" t="s">
-        <v>117</v>
       </c>
       <c r="D176" s="121"/>
       <c r="E176" s="122"/>
@@ -7180,13 +7180,13 @@
         <v>34</v>
       </c>
       <c r="C177" s="120" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D177" s="121"/>
       <c r="E177" s="122"/>
       <c r="F177" s="119"/>
       <c r="G177" s="119" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H177" s="123"/>
       <c r="I177" s="119"/>
@@ -7221,10 +7221,10 @@
     <row r="178" spans="1:36" s="105" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A178" s="119"/>
       <c r="B178" s="119" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C178" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D178" s="121"/>
       <c r="E178" s="122"/>
@@ -7263,10 +7263,10 @@
     <row r="179" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="119"/>
       <c r="B179" s="119" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C179" s="120" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D179" s="121"/>
       <c r="E179" s="122"/>
@@ -7305,10 +7305,10 @@
     <row r="180" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="119"/>
       <c r="B180" s="119" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C180" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D180" s="121"/>
       <c r="E180" s="122"/>
@@ -7347,10 +7347,10 @@
     <row r="181" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="119"/>
       <c r="B181" s="119" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C181" s="120" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D181" s="121"/>
       <c r="E181" s="122"/>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="183" spans="1:36" s="78" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="197" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B183" s="198"/>
       <c r="C183" s="198"/>
@@ -7528,7 +7528,7 @@
         <v>9</v>
       </c>
       <c r="C185" s="125" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D185" s="126"/>
       <c r="E185" s="127"/>
@@ -7576,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C186" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D186" s="121"/>
       <c r="E186" s="122"/>
@@ -7619,10 +7619,10 @@
         <v>3</v>
       </c>
       <c r="B187" s="119" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C187" s="120" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D187" s="121"/>
       <c r="E187" s="122"/>
@@ -7663,10 +7663,10 @@
         <v>4</v>
       </c>
       <c r="B188" s="119" t="s">
+        <v>131</v>
+      </c>
+      <c r="C188" s="120" t="s">
         <v>132</v>
-      </c>
-      <c r="C188" s="120" t="s">
-        <v>133</v>
       </c>
       <c r="D188" s="121"/>
       <c r="E188" s="122"/>
@@ -7707,10 +7707,10 @@
         <v>5</v>
       </c>
       <c r="B189" s="119" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C189" s="120" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D189" s="121"/>
       <c r="E189" s="122"/>
@@ -7751,10 +7751,10 @@
         <v>6</v>
       </c>
       <c r="B190" s="119" t="s">
+        <v>133</v>
+      </c>
+      <c r="C190" s="120" t="s">
         <v>134</v>
-      </c>
-      <c r="C190" s="120" t="s">
-        <v>135</v>
       </c>
       <c r="D190" s="121"/>
       <c r="E190" s="122"/>
@@ -28529,16 +28529,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="162" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C1" s="169" t="s">
         <v>37</v>
       </c>
       <c r="D1" s="169" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E1" s="169" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F1" s="55"/>
       <c r="G1" s="55"/>
@@ -28567,7 +28567,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2" s="170"/>
       <c r="D2" s="170"/>
@@ -28599,7 +28599,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="163" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="170"/>
       <c r="D3" s="170"/>
@@ -28631,7 +28631,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="163" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="170"/>
       <c r="D4" s="170"/>
@@ -28663,7 +28663,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="163" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="170"/>
       <c r="D5" s="170"/>
@@ -28695,7 +28695,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="163" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" s="170"/>
       <c r="D6" s="170"/>
@@ -28727,7 +28727,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="170"/>
       <c r="D7" s="170"/>
@@ -28795,7 +28795,7 @@
       </c>
       <c r="C9" s="170"/>
       <c r="D9" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E9" s="170"/>
       <c r="F9" s="54"/>
@@ -28822,14 +28822,14 @@
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="85" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B10" s="164" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" s="170"/>
       <c r="D10" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E10" s="170"/>
       <c r="F10" s="54"/>
@@ -28856,14 +28856,14 @@
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="85" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B11" s="164" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C11" s="170"/>
       <c r="D11" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E11" s="170"/>
       <c r="F11" s="54"/>
@@ -28893,11 +28893,11 @@
         <v>2</v>
       </c>
       <c r="B12" s="164" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C12" s="170"/>
       <c r="D12" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E12" s="170"/>
       <c r="F12" s="54"/>
@@ -28924,14 +28924,14 @@
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="85" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B13" s="164" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C13" s="170"/>
       <c r="D13" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E13" s="170"/>
       <c r="F13" s="54"/>
@@ -28958,14 +28958,14 @@
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B14" s="164" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E14" s="170"/>
       <c r="F14" s="54"/>
@@ -28995,11 +28995,11 @@
         <v>3</v>
       </c>
       <c r="B15" s="164" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C15" s="170"/>
       <c r="D15" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E15" s="170"/>
       <c r="F15" s="54"/>
@@ -29026,14 +29026,14 @@
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="85" t="s">
+        <v>198</v>
+      </c>
+      <c r="B16" s="164" t="s">
         <v>199</v>
-      </c>
-      <c r="B16" s="164" t="s">
-        <v>200</v>
       </c>
       <c r="C16" s="170"/>
       <c r="D16" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" s="170"/>
       <c r="F16" s="54"/>
@@ -29060,14 +29060,14 @@
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B17" s="164" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C17" s="170"/>
       <c r="D17" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E17" s="170"/>
       <c r="F17" s="54"/>
@@ -29094,14 +29094,14 @@
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="85" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B18" s="164" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C18" s="170"/>
       <c r="D18" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E18" s="170"/>
       <c r="F18" s="54"/>
@@ -29128,14 +29128,14 @@
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="85" t="s">
+        <v>202</v>
+      </c>
+      <c r="B19" s="164" t="s">
         <v>203</v>
-      </c>
-      <c r="B19" s="164" t="s">
-        <v>204</v>
       </c>
       <c r="C19" s="170"/>
       <c r="D19" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E19" s="170"/>
       <c r="F19" s="54"/>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="C20" s="170"/>
       <c r="D20" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E20" s="170"/>
       <c r="F20" s="54"/>
@@ -29203,7 +29203,7 @@
       </c>
       <c r="C21" s="170"/>
       <c r="D21" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E21" s="170"/>
       <c r="F21" s="54"/>
@@ -29230,14 +29230,14 @@
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="173" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B22" s="165" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C22" s="170"/>
       <c r="D22" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="170"/>
       <c r="F22" s="54"/>
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C23" s="170"/>
       <c r="D23" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" s="170"/>
       <c r="F23" s="54"/>
@@ -29305,7 +29305,7 @@
       </c>
       <c r="C24" s="170"/>
       <c r="D24" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E24" s="170"/>
       <c r="F24" s="54"/>
@@ -29332,14 +29332,14 @@
     </row>
     <row r="25" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A25" s="75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B25" s="166" t="s">
         <v>58</v>
       </c>
       <c r="C25" s="170"/>
       <c r="D25" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E25" s="170"/>
       <c r="F25" s="54"/>
@@ -29366,14 +29366,14 @@
     </row>
     <row r="26" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A26" s="75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B26" s="166" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C26" s="170"/>
       <c r="D26" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E26" s="170"/>
       <c r="F26" s="54"/>
@@ -29400,14 +29400,14 @@
     </row>
     <row r="27" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A27" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" s="166" t="s">
         <v>197</v>
-      </c>
-      <c r="B27" s="166" t="s">
-        <v>198</v>
       </c>
       <c r="C27" s="170"/>
       <c r="D27" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E27" s="170"/>
       <c r="F27" s="54"/>
@@ -29441,7 +29441,7 @@
       </c>
       <c r="C28" s="170"/>
       <c r="D28" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E28" s="170"/>
       <c r="F28" s="54"/>
@@ -29475,7 +29475,7 @@
       </c>
       <c r="C29" s="170"/>
       <c r="D29" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E29" s="170"/>
       <c r="F29" s="54"/>
@@ -29509,7 +29509,7 @@
       </c>
       <c r="C30" s="170"/>
       <c r="D30" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E30" s="170"/>
       <c r="F30" s="54"/>
@@ -29543,7 +29543,7 @@
       </c>
       <c r="C31" s="170"/>
       <c r="D31" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E31" s="170"/>
       <c r="F31" s="54"/>
@@ -29577,7 +29577,7 @@
       </c>
       <c r="C32" s="170"/>
       <c r="D32" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E32" s="170"/>
       <c r="F32" s="54"/>
@@ -29611,7 +29611,7 @@
       </c>
       <c r="C33" s="170"/>
       <c r="D33" s="170" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E33" s="170"/>
       <c r="F33" s="54"/>
@@ -29641,14 +29641,14 @@
         <v>15</v>
       </c>
       <c r="B34" s="168" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C34" s="170"/>
       <c r="D34" s="170" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" s="170" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F34" s="54"/>
       <c r="G34" s="54"/>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="C35" s="170"/>
       <c r="D35" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E35" s="170"/>
       <c r="F35" s="54"/>
@@ -29715,7 +29715,7 @@
       </c>
       <c r="C36" s="170"/>
       <c r="D36" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E36" s="170"/>
       <c r="F36" s="54"/>
@@ -29749,7 +29749,7 @@
       </c>
       <c r="C37" s="190"/>
       <c r="D37" s="190" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E37" s="190"/>
       <c r="F37" s="111"/>
@@ -29783,7 +29783,7 @@
       </c>
       <c r="C38" s="170"/>
       <c r="D38" s="170" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E38" s="170"/>
       <c r="F38" s="54"/>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="C39" s="170"/>
       <c r="D39" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E39" s="170"/>
       <c r="F39" s="54"/>
@@ -29911,7 +29911,7 @@
         <v>23</v>
       </c>
       <c r="B42" s="168" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C42" s="170"/>
       <c r="D42" s="170"/>
@@ -29943,7 +29943,7 @@
         <v>24</v>
       </c>
       <c r="B43" s="168" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C43" s="170"/>
       <c r="D43" s="170"/>
@@ -29979,7 +29979,7 @@
       </c>
       <c r="C44" s="170"/>
       <c r="D44" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E44" s="170"/>
       <c r="F44" s="54"/>
@@ -30013,7 +30013,7 @@
       </c>
       <c r="C45" s="193"/>
       <c r="D45" s="193" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E45" s="193"/>
       <c r="F45" s="194"/>
@@ -30048,7 +30048,7 @@
       <c r="C46" s="170"/>
       <c r="D46" s="170"/>
       <c r="E46" s="170" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F46" s="54"/>
       <c r="G46" s="54"/>
@@ -30109,12 +30109,12 @@
         <v>29</v>
       </c>
       <c r="B48" s="168" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="C48" s="170"/>
       <c r="D48" s="170"/>
       <c r="E48" s="170" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F48" s="54"/>
       <c r="G48" s="54"/>
@@ -30143,12 +30143,12 @@
         <v>30</v>
       </c>
       <c r="B49" s="168" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C49" s="170"/>
       <c r="D49" s="170"/>
       <c r="E49" s="170" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F49" s="54"/>
       <c r="G49" s="54"/>
@@ -30177,7 +30177,7 @@
         <v>31</v>
       </c>
       <c r="B50" s="168" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C50" s="170"/>
       <c r="D50" s="170"/>
@@ -30209,7 +30209,7 @@
         <v>32</v>
       </c>
       <c r="B51" s="168" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C51" s="170"/>
       <c r="D51" s="170"/>
@@ -30241,7 +30241,7 @@
         <v>33</v>
       </c>
       <c r="B52" s="168" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C52" s="170"/>
       <c r="D52" s="170"/>
@@ -30273,7 +30273,7 @@
         <v>34</v>
       </c>
       <c r="B53" s="168" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C53" s="170"/>
       <c r="D53" s="170"/>
@@ -57340,7 +57340,7 @@
   <sheetData>
     <row r="3" spans="1:13" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A3" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B3" s="198"/>
       <c r="C3" s="198"/>
@@ -57388,7 +57388,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="63"/>
       <c r="E5" s="64"/>
@@ -57409,7 +57409,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D6" s="69"/>
       <c r="E6" s="70"/>
@@ -57425,10 +57425,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" s="69"/>
       <c r="E7" s="70"/>
@@ -57437,7 +57437,7 @@
       <c r="H7" s="71"/>
       <c r="I7" s="67"/>
       <c r="L7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.45" x14ac:dyDescent="0.4">
@@ -57445,10 +57445,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="67" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="68" t="s">
         <v>138</v>
-      </c>
-      <c r="C8" s="68" t="s">
-        <v>139</v>
       </c>
       <c r="D8" s="69"/>
       <c r="E8" s="70"/>
@@ -57462,10 +57462,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" s="69"/>
       <c r="E9" s="70"/>
@@ -57473,10 +57473,10 @@
       <c r="G9" s="67"/>
       <c r="H9" s="71"/>
       <c r="I9" s="67" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L9" s="73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M9" s="74"/>
     </row>
@@ -57490,10 +57490,10 @@
       <c r="G10" s="67"/>
       <c r="H10" s="71"/>
       <c r="I10" s="67" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L10" s="73" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M10" s="74"/>
     </row>
@@ -57520,36 +57520,36 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="L14" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="M14" s="74" t="s">
         <v>156</v>
-      </c>
-      <c r="M14" s="74" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" t="s">
         <v>147</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>148</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>149</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>150</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>151</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>152</v>
       </c>
-      <c r="J15" t="s">
-        <v>153</v>
-      </c>
       <c r="L15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M15">
         <v>15</v>
@@ -57557,117 +57557,117 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="D16" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E16" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F16" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G16" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H16" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I16" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J16" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D18" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E18" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F18" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G18" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H18" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I18" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J18" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D20" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E20" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F20" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G20" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H20" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I20" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J20" s="73" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/Database Design & Questions.xlsx
+++ b/Database Design & Questions.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="210">
   <si>
     <t>No.</t>
   </si>
@@ -263,9 +263,6 @@
   </si>
   <si>
     <t>Hiển thị tất cả danh mục (Categories) với tổng số tiền bán được trong mỗi danh mục</t>
-  </si>
-  <si>
-    <t>Hiển thị tất cả đơn hàng với tổng số tiền mà đã được giao hàng thành công trong khoảng từ ngày, đến ngày</t>
   </si>
   <si>
     <t>Hiển thị tất cả đơn hàng có tổng số tiền bán hàng ít nhất trong khoảng từ ngày, đến ngày</t>
@@ -659,6 +656,12 @@
   </si>
   <si>
     <t>Hiển thị danh sách các mức giảm giá của sản phẩm</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả đơn hàng với tổng số tiền trong khoảng từ ngày, đến ngày</t>
+  </si>
+  <si>
+    <t>Hiển thị tất cả các khách hàng không mua hàng trong khoảng từ ngày, đến ngày</t>
   </si>
 </sst>
 </file>
@@ -1841,7 +1844,7 @@
     <row r="2" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="76" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1870,7 +1873,7 @@
     </row>
     <row r="3" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
@@ -1952,7 +1955,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
@@ -1990,7 +1993,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="7">
         <v>50</v>
@@ -2023,10 +2026,10 @@
     <row r="7" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="79"/>
       <c r="B7" s="80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" s="82"/>
       <c r="E7" s="81"/>
@@ -2062,7 +2065,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" s="7">
         <v>500</v>
@@ -2097,10 +2100,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="130" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="131" t="s">
         <v>117</v>
-      </c>
-      <c r="C9" s="131" t="s">
-        <v>118</v>
       </c>
       <c r="D9" s="130"/>
       <c r="E9" s="131"/>
@@ -2108,10 +2111,10 @@
       <c r="G9" s="130"/>
       <c r="H9" s="130"/>
       <c r="I9" s="130" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J9" s="118" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K9" s="118"/>
       <c r="L9" s="118"/>
@@ -2135,10 +2138,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="133" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" s="134" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" s="133"/>
       <c r="E10" s="134"/>
@@ -2169,10 +2172,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="134" t="s">
         <v>112</v>
-      </c>
-      <c r="C11" s="134" t="s">
-        <v>113</v>
       </c>
       <c r="D11" s="133"/>
       <c r="E11" s="134"/>
@@ -2203,10 +2206,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="133" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="134" t="s">
         <v>115</v>
-      </c>
-      <c r="C12" s="134" t="s">
-        <v>116</v>
       </c>
       <c r="D12" s="133"/>
       <c r="E12" s="134"/>
@@ -2237,10 +2240,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="133" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" s="133"/>
       <c r="E13" s="134"/>
@@ -2274,7 +2277,7 @@
         <v>34</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D14" s="133"/>
       <c r="E14" s="134"/>
@@ -2305,10 +2308,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="133" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C15" s="134" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D15" s="133"/>
       <c r="E15" s="134"/>
@@ -2339,10 +2342,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="133" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="134" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16" s="133"/>
       <c r="E16" s="134"/>
@@ -2373,10 +2376,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="133" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C17" s="134" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D17" s="133"/>
       <c r="E17" s="134"/>
@@ -2432,7 +2435,7 @@
     </row>
     <row r="19" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="196" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B19" s="196"/>
       <c r="C19" s="196"/>
@@ -2514,7 +2517,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
@@ -2552,7 +2555,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D22" s="17">
         <v>100</v>
@@ -2588,7 +2591,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D23" s="17">
         <v>50</v>
@@ -2626,7 +2629,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D24" s="17">
         <v>50</v>
@@ -2661,10 +2664,10 @@
     <row r="25" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="79"/>
       <c r="B25" s="80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D25" s="82"/>
       <c r="E25" s="81"/>
@@ -2700,7 +2703,7 @@
         <v>18</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D26" s="17">
         <v>500</v>
@@ -2758,7 +2761,7 @@
     </row>
     <row r="28" spans="1:26" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="196" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28" s="196"/>
       <c r="C28" s="196"/>
@@ -2840,7 +2843,7 @@
         <v>9</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" s="24">
         <v>50</v>
@@ -2878,7 +2881,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" s="28">
         <v>50</v>
@@ -2914,7 +2917,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D32" s="28">
         <v>50</v>
@@ -2950,7 +2953,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D33" s="28">
         <v>50</v>
@@ -2988,7 +2991,7 @@
         <v>18</v>
       </c>
       <c r="C34" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="28">
         <v>500</v>
@@ -3026,7 +3029,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D35" s="93">
         <v>50</v>
@@ -3059,10 +3062,10 @@
     <row r="36" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="79"/>
       <c r="B36" s="80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D36" s="82"/>
       <c r="E36" s="81"/>
@@ -3131,10 +3134,10 @@
         <v>8</v>
       </c>
       <c r="B38" s="92" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D38" s="93"/>
       <c r="E38" s="94"/>
@@ -3165,10 +3168,10 @@
         <v>9</v>
       </c>
       <c r="B39" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="C39" s="137" t="s">
         <v>131</v>
-      </c>
-      <c r="C39" s="137" t="s">
-        <v>132</v>
       </c>
       <c r="D39" s="138"/>
       <c r="E39" s="139"/>
@@ -3199,10 +3202,10 @@
         <v>10</v>
       </c>
       <c r="B40" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C40" s="137" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D40" s="138"/>
       <c r="E40" s="139"/>
@@ -3258,7 +3261,7 @@
     </row>
     <row r="42" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="199" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B42" s="200"/>
       <c r="C42" s="200"/>
@@ -3340,7 +3343,7 @@
         <v>9</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D44" s="32">
         <v>50</v>
@@ -3378,7 +3381,7 @@
         <v>19</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D45" s="36">
         <v>50</v>
@@ -3414,7 +3417,7 @@
         <v>20</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D46" s="36">
         <v>50</v>
@@ -3450,7 +3453,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D47" s="36">
         <v>50</v>
@@ -3488,7 +3491,7 @@
         <v>18</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D48" s="36">
         <v>500</v>
@@ -3526,7 +3529,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="96" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D49" s="97">
         <v>50</v>
@@ -3559,10 +3562,10 @@
     <row r="50" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="79"/>
       <c r="B50" s="80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D50" s="82"/>
       <c r="E50" s="81"/>
@@ -3631,10 +3634,10 @@
         <v>8</v>
       </c>
       <c r="B52" s="92" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D52" s="93"/>
       <c r="E52" s="94"/>
@@ -3665,10 +3668,10 @@
         <v>9</v>
       </c>
       <c r="B53" s="136" t="s">
+        <v>130</v>
+      </c>
+      <c r="C53" s="137" t="s">
         <v>131</v>
-      </c>
-      <c r="C53" s="137" t="s">
-        <v>132</v>
       </c>
       <c r="D53" s="138"/>
       <c r="E53" s="139"/>
@@ -3699,10 +3702,10 @@
         <v>10</v>
       </c>
       <c r="B54" s="136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C54" s="137" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D54" s="138"/>
       <c r="E54" s="139"/>
@@ -3758,7 +3761,7 @@
     </row>
     <row r="56" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="202" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B56" s="202"/>
       <c r="C56" s="202"/>
@@ -3840,7 +3843,7 @@
         <v>9</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D58" s="41"/>
       <c r="E58" s="42"/>
@@ -3878,7 +3881,7 @@
         <v>12</v>
       </c>
       <c r="C59" s="44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D59" s="45">
         <v>50</v>
@@ -3961,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I61" s="43"/>
       <c r="J61" s="77"/>
@@ -4026,7 +4029,7 @@
         <v>28</v>
       </c>
       <c r="C63" s="182" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D63" s="183"/>
       <c r="E63" s="184"/>
@@ -4064,7 +4067,7 @@
         <v>31</v>
       </c>
       <c r="C64" s="182" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D64" s="183"/>
       <c r="E64" s="184"/>
@@ -4102,7 +4105,7 @@
         <v>14</v>
       </c>
       <c r="C65" s="81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D65" s="82">
         <v>3000</v>
@@ -4135,10 +4138,10 @@
         <v>9</v>
       </c>
       <c r="B66" s="80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C66" s="81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D66" s="82"/>
       <c r="E66" s="81"/>
@@ -4171,10 +4174,10 @@
         <v>10</v>
       </c>
       <c r="B67" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="C67" s="100" t="s">
         <v>117</v>
-      </c>
-      <c r="C67" s="100" t="s">
-        <v>118</v>
       </c>
       <c r="D67" s="101"/>
       <c r="E67" s="100"/>
@@ -4182,7 +4185,7 @@
       <c r="G67" s="99"/>
       <c r="H67" s="102"/>
       <c r="I67" s="99" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J67" s="103"/>
       <c r="K67" s="103"/>
@@ -4207,10 +4210,10 @@
         <v>11</v>
       </c>
       <c r="B68" s="99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C68" s="104" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D68" s="101"/>
       <c r="E68" s="100"/>
@@ -4241,10 +4244,10 @@
         <v>12</v>
       </c>
       <c r="B69" s="99" t="s">
+        <v>124</v>
+      </c>
+      <c r="C69" s="100" t="s">
         <v>125</v>
-      </c>
-      <c r="C69" s="100" t="s">
-        <v>126</v>
       </c>
       <c r="D69" s="101"/>
       <c r="E69" s="100"/>
@@ -4252,7 +4255,7 @@
       <c r="G69" s="99"/>
       <c r="H69" s="102"/>
       <c r="I69" s="99" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J69" s="103"/>
       <c r="K69" s="103"/>
@@ -4302,7 +4305,7 @@
     </row>
     <row r="71" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="203" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B71" s="204"/>
       <c r="C71" s="204"/>
@@ -4384,7 +4387,7 @@
         <v>9</v>
       </c>
       <c r="C73" s="142" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D73" s="143"/>
       <c r="E73" s="144"/>
@@ -4428,7 +4431,7 @@
       <c r="E74" s="148"/>
       <c r="F74" s="149"/>
       <c r="G74" s="145" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H74" s="145" t="s">
         <v>35</v>
@@ -4498,7 +4501,7 @@
         <v>37</v>
       </c>
       <c r="C76" s="146" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D76" s="150">
         <v>50</v>
@@ -4538,7 +4541,7 @@
         <v>14</v>
       </c>
       <c r="C77" s="146" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D77" s="150" t="s">
         <v>33</v>
@@ -4576,7 +4579,7 @@
         <v>40</v>
       </c>
       <c r="C78" s="146" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D78" s="150">
         <v>500</v>
@@ -4612,7 +4615,7 @@
         <v>41</v>
       </c>
       <c r="C79" s="146" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D79" s="150">
         <v>20</v>
@@ -4623,7 +4626,7 @@
         <v>42</v>
       </c>
       <c r="H79" s="145" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I79" s="145"/>
       <c r="J79" s="77"/>
@@ -4652,7 +4655,7 @@
         <v>43</v>
       </c>
       <c r="C80" s="146" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D80" s="150">
         <v>50</v>
@@ -4687,10 +4690,10 @@
     <row r="81" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="79"/>
       <c r="B81" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="C81" s="81" t="s">
         <v>185</v>
-      </c>
-      <c r="C81" s="81" t="s">
-        <v>186</v>
       </c>
       <c r="D81" s="82"/>
       <c r="E81" s="81"/>
@@ -4719,10 +4722,10 @@
     <row r="82" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="79"/>
       <c r="B82" s="80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C82" s="81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D82" s="82"/>
       <c r="E82" s="81"/>
@@ -4755,10 +4758,10 @@
         <v>9</v>
       </c>
       <c r="B83" s="145" t="s">
+        <v>187</v>
+      </c>
+      <c r="C83" s="146" t="s">
         <v>188</v>
-      </c>
-      <c r="C83" s="146" t="s">
-        <v>189</v>
       </c>
       <c r="D83" s="150">
         <v>50</v>
@@ -4800,7 +4803,7 @@
         <v>45</v>
       </c>
       <c r="C84" s="146" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D84" s="150">
         <v>50</v>
@@ -4839,10 +4842,10 @@
         <v>10</v>
       </c>
       <c r="B85" s="106" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="107" t="s">
         <v>120</v>
-      </c>
-      <c r="C85" s="107" t="s">
-        <v>121</v>
       </c>
       <c r="D85" s="108"/>
       <c r="E85" s="109"/>
@@ -4887,10 +4890,10 @@
         <v>11</v>
       </c>
       <c r="B86" s="106" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C86" s="107" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D86" s="108"/>
       <c r="E86" s="109"/>
@@ -4935,10 +4938,10 @@
         <v>12</v>
       </c>
       <c r="B87" s="106" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C87" s="107" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D87" s="108"/>
       <c r="E87" s="109"/>
@@ -5008,7 +5011,7 @@
     </row>
     <row r="89" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="205" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B89" s="204"/>
       <c r="C89" s="204"/>
@@ -5090,7 +5093,7 @@
         <v>9</v>
       </c>
       <c r="C91" s="154" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D91" s="155"/>
       <c r="E91" s="156"/>
@@ -5128,7 +5131,7 @@
         <v>47</v>
       </c>
       <c r="C92" s="159" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D92" s="160"/>
       <c r="E92" s="161"/>
@@ -5229,10 +5232,10 @@
     <row r="95" spans="1:40" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="79"/>
       <c r="B95" s="80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C95" s="81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D95" s="82"/>
       <c r="E95" s="81"/>
@@ -5268,7 +5271,7 @@
         <v>25</v>
       </c>
       <c r="C96" s="159" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D96" s="160"/>
       <c r="E96" s="161"/>
@@ -5324,7 +5327,7 @@
     </row>
     <row r="98" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="203" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B98" s="204"/>
       <c r="C98" s="204"/>
@@ -5406,7 +5409,7 @@
         <v>9</v>
       </c>
       <c r="C100" s="142" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D100" s="143"/>
       <c r="E100" s="144"/>
@@ -5439,10 +5442,10 @@
     <row r="101" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="79"/>
       <c r="B101" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="C101" s="81" t="s">
         <v>185</v>
-      </c>
-      <c r="C101" s="81" t="s">
-        <v>186</v>
       </c>
       <c r="D101" s="82"/>
       <c r="E101" s="81"/>
@@ -5476,7 +5479,7 @@
         <v>43</v>
       </c>
       <c r="C102" s="146" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D102" s="150">
         <v>50</v>
@@ -5538,7 +5541,7 @@
     </row>
     <row r="104" spans="1:26" s="78" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="205" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B104" s="204"/>
       <c r="C104" s="204"/>
@@ -5620,7 +5623,7 @@
         <v>9</v>
       </c>
       <c r="C106" s="154" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D106" s="155"/>
       <c r="E106" s="156"/>
@@ -5658,7 +5661,7 @@
         <v>47</v>
       </c>
       <c r="C107" s="159" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D107" s="160"/>
       <c r="E107" s="161"/>
@@ -6322,7 +6325,7 @@
     </row>
     <row r="158" spans="1:36" s="78" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A158" s="197" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B158" s="198"/>
       <c r="C158" s="198"/>
@@ -6414,7 +6417,7 @@
         <v>9</v>
       </c>
       <c r="C160" s="113" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D160" s="114"/>
       <c r="E160" s="115"/>
@@ -6459,10 +6462,10 @@
         <v>2</v>
       </c>
       <c r="B161" s="119" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C161" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D161" s="121"/>
       <c r="E161" s="122"/>
@@ -6503,14 +6506,14 @@
         <v>3</v>
       </c>
       <c r="B162" s="119" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C162" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D162" s="121"/>
       <c r="E162" s="122" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F162" s="119"/>
       <c r="G162" s="119"/>
@@ -6549,10 +6552,10 @@
         <v>4</v>
       </c>
       <c r="B163" s="119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C163" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D163" s="121"/>
       <c r="E163" s="122"/>
@@ -6593,10 +6596,10 @@
         <v>5</v>
       </c>
       <c r="B164" s="119" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C164" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D164" s="121"/>
       <c r="E164" s="122"/>
@@ -6637,10 +6640,10 @@
         <v>6</v>
       </c>
       <c r="B165" s="119" t="s">
+        <v>111</v>
+      </c>
+      <c r="C165" s="120" t="s">
         <v>112</v>
-      </c>
-      <c r="C165" s="120" t="s">
-        <v>113</v>
       </c>
       <c r="D165" s="121"/>
       <c r="E165" s="122"/>
@@ -6648,7 +6651,7 @@
       <c r="G165" s="119"/>
       <c r="H165" s="123"/>
       <c r="I165" s="119" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J165" s="77"/>
       <c r="K165" s="77"/>
@@ -6683,10 +6686,10 @@
         <v>7</v>
       </c>
       <c r="B166" s="119" t="s">
+        <v>114</v>
+      </c>
+      <c r="C166" s="120" t="s">
         <v>115</v>
-      </c>
-      <c r="C166" s="120" t="s">
-        <v>116</v>
       </c>
       <c r="D166" s="121"/>
       <c r="E166" s="122"/>
@@ -6762,7 +6765,7 @@
     </row>
     <row r="168" spans="1:36" s="78" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A168" s="197" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B168" s="198"/>
       <c r="C168" s="198"/>
@@ -6864,7 +6867,7 @@
         <v>9</v>
       </c>
       <c r="C170" s="125" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D170" s="126"/>
       <c r="E170" s="127"/>
@@ -6909,10 +6912,10 @@
         <v>2</v>
       </c>
       <c r="B171" s="119" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C171" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D171" s="121"/>
       <c r="E171" s="122"/>
@@ -6953,14 +6956,14 @@
         <v>3</v>
       </c>
       <c r="B172" s="119" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C172" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D172" s="121"/>
       <c r="E172" s="122" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F172" s="119"/>
       <c r="G172" s="119"/>
@@ -6999,10 +7002,10 @@
         <v>4</v>
       </c>
       <c r="B173" s="119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C173" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D173" s="121"/>
       <c r="E173" s="122"/>
@@ -7043,10 +7046,10 @@
         <v>5</v>
       </c>
       <c r="B174" s="119" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C174" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D174" s="121"/>
       <c r="E174" s="122"/>
@@ -7087,10 +7090,10 @@
         <v>6</v>
       </c>
       <c r="B175" s="119" t="s">
+        <v>111</v>
+      </c>
+      <c r="C175" s="120" t="s">
         <v>112</v>
-      </c>
-      <c r="C175" s="120" t="s">
-        <v>113</v>
       </c>
       <c r="D175" s="121"/>
       <c r="E175" s="122"/>
@@ -7098,7 +7101,7 @@
       <c r="G175" s="119"/>
       <c r="H175" s="123"/>
       <c r="I175" s="119" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J175" s="77"/>
       <c r="K175" s="77"/>
@@ -7133,10 +7136,10 @@
         <v>7</v>
       </c>
       <c r="B176" s="119" t="s">
+        <v>114</v>
+      </c>
+      <c r="C176" s="120" t="s">
         <v>115</v>
-      </c>
-      <c r="C176" s="120" t="s">
-        <v>116</v>
       </c>
       <c r="D176" s="121"/>
       <c r="E176" s="122"/>
@@ -7180,13 +7183,13 @@
         <v>34</v>
       </c>
       <c r="C177" s="120" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D177" s="121"/>
       <c r="E177" s="122"/>
       <c r="F177" s="119"/>
       <c r="G177" s="119" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H177" s="123"/>
       <c r="I177" s="119"/>
@@ -7221,10 +7224,10 @@
     <row r="178" spans="1:36" s="105" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A178" s="119"/>
       <c r="B178" s="119" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C178" s="120" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D178" s="121"/>
       <c r="E178" s="122"/>
@@ -7263,10 +7266,10 @@
     <row r="179" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A179" s="119"/>
       <c r="B179" s="119" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C179" s="120" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D179" s="121"/>
       <c r="E179" s="122"/>
@@ -7305,10 +7308,10 @@
     <row r="180" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A180" s="119"/>
       <c r="B180" s="119" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C180" s="120" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D180" s="121"/>
       <c r="E180" s="122"/>
@@ -7347,10 +7350,10 @@
     <row r="181" spans="1:36" s="73" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A181" s="119"/>
       <c r="B181" s="119" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C181" s="120" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D181" s="121"/>
       <c r="E181" s="122"/>
@@ -7426,7 +7429,7 @@
     </row>
     <row r="183" spans="1:36" s="78" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A183" s="197" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B183" s="198"/>
       <c r="C183" s="198"/>
@@ -7528,7 +7531,7 @@
         <v>9</v>
       </c>
       <c r="C185" s="125" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D185" s="126"/>
       <c r="E185" s="127"/>
@@ -7576,7 +7579,7 @@
         <v>16</v>
       </c>
       <c r="C186" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D186" s="121"/>
       <c r="E186" s="122"/>
@@ -7619,10 +7622,10 @@
         <v>3</v>
       </c>
       <c r="B187" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C187" s="120" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D187" s="121"/>
       <c r="E187" s="122"/>
@@ -7663,10 +7666,10 @@
         <v>4</v>
       </c>
       <c r="B188" s="119" t="s">
+        <v>130</v>
+      </c>
+      <c r="C188" s="120" t="s">
         <v>131</v>
-      </c>
-      <c r="C188" s="120" t="s">
-        <v>132</v>
       </c>
       <c r="D188" s="121"/>
       <c r="E188" s="122"/>
@@ -7707,10 +7710,10 @@
         <v>5</v>
       </c>
       <c r="B189" s="119" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C189" s="120" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D189" s="121"/>
       <c r="E189" s="122"/>
@@ -7751,10 +7754,10 @@
         <v>6</v>
       </c>
       <c r="B190" s="119" t="s">
+        <v>132</v>
+      </c>
+      <c r="C190" s="120" t="s">
         <v>133</v>
-      </c>
-      <c r="C190" s="120" t="s">
-        <v>134</v>
       </c>
       <c r="D190" s="121"/>
       <c r="E190" s="122"/>
@@ -28529,16 +28532,16 @@
         <v>50</v>
       </c>
       <c r="B1" s="162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C1" s="169" t="s">
         <v>37</v>
       </c>
       <c r="D1" s="169" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" s="169" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F1" s="55"/>
       <c r="G1" s="55"/>
@@ -28567,7 +28570,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" s="170"/>
       <c r="D2" s="170"/>
@@ -28599,7 +28602,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3" s="170"/>
       <c r="D3" s="170"/>
@@ -28631,7 +28634,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="163" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="170"/>
       <c r="D4" s="170"/>
@@ -28663,7 +28666,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="163" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="170"/>
       <c r="D5" s="170"/>
@@ -28695,7 +28698,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="163" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="170"/>
       <c r="D6" s="170"/>
@@ -28727,7 +28730,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="170"/>
       <c r="D7" s="170"/>
@@ -28795,7 +28798,7 @@
       </c>
       <c r="C9" s="170"/>
       <c r="D9" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E9" s="170"/>
       <c r="F9" s="54"/>
@@ -28822,14 +28825,14 @@
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="85" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B10" s="164" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C10" s="170"/>
       <c r="D10" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E10" s="170"/>
       <c r="F10" s="54"/>
@@ -28856,14 +28859,14 @@
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="85" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B11" s="164" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C11" s="170"/>
       <c r="D11" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E11" s="170"/>
       <c r="F11" s="54"/>
@@ -28893,11 +28896,11 @@
         <v>2</v>
       </c>
       <c r="B12" s="164" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C12" s="170"/>
       <c r="D12" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E12" s="170"/>
       <c r="F12" s="54"/>
@@ -28924,14 +28927,14 @@
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="85" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B13" s="164" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C13" s="170"/>
       <c r="D13" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E13" s="170"/>
       <c r="F13" s="54"/>
@@ -28958,14 +28961,14 @@
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="85" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B14" s="164" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E14" s="170"/>
       <c r="F14" s="54"/>
@@ -28995,11 +28998,11 @@
         <v>3</v>
       </c>
       <c r="B15" s="164" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C15" s="170"/>
       <c r="D15" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E15" s="170"/>
       <c r="F15" s="54"/>
@@ -29026,14 +29029,14 @@
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="85" t="s">
+        <v>197</v>
+      </c>
+      <c r="B16" s="164" t="s">
         <v>198</v>
-      </c>
-      <c r="B16" s="164" t="s">
-        <v>199</v>
       </c>
       <c r="C16" s="170"/>
       <c r="D16" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" s="170"/>
       <c r="F16" s="54"/>
@@ -29060,14 +29063,14 @@
     </row>
     <row r="17" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="85" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B17" s="164" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C17" s="170"/>
       <c r="D17" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E17" s="170"/>
       <c r="F17" s="54"/>
@@ -29094,14 +29097,14 @@
     </row>
     <row r="18" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B18" s="164" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C18" s="170"/>
       <c r="D18" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E18" s="170"/>
       <c r="F18" s="54"/>
@@ -29128,14 +29131,14 @@
     </row>
     <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="85" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" s="164" t="s">
         <v>202</v>
-      </c>
-      <c r="B19" s="164" t="s">
-        <v>203</v>
       </c>
       <c r="C19" s="170"/>
       <c r="D19" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E19" s="170"/>
       <c r="F19" s="54"/>
@@ -29169,7 +29172,7 @@
       </c>
       <c r="C20" s="170"/>
       <c r="D20" s="170" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E20" s="170"/>
       <c r="F20" s="54"/>
@@ -29203,7 +29206,7 @@
       </c>
       <c r="C21" s="170"/>
       <c r="D21" s="170" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="170"/>
       <c r="F21" s="54"/>
@@ -29230,14 +29233,14 @@
     </row>
     <row r="22" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="173" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B22" s="165" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C22" s="170"/>
       <c r="D22" s="170" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" s="170"/>
       <c r="F22" s="54"/>
@@ -29271,7 +29274,7 @@
       </c>
       <c r="C23" s="170"/>
       <c r="D23" s="170" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" s="170"/>
       <c r="F23" s="54"/>
@@ -29305,7 +29308,7 @@
       </c>
       <c r="C24" s="170"/>
       <c r="D24" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E24" s="170"/>
       <c r="F24" s="54"/>
@@ -29332,14 +29335,14 @@
     </row>
     <row r="25" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A25" s="75" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B25" s="166" t="s">
         <v>58</v>
       </c>
       <c r="C25" s="170"/>
       <c r="D25" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E25" s="170"/>
       <c r="F25" s="54"/>
@@ -29366,14 +29369,14 @@
     </row>
     <row r="26" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A26" s="75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B26" s="166" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C26" s="170"/>
       <c r="D26" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E26" s="170"/>
       <c r="F26" s="54"/>
@@ -29400,14 +29403,14 @@
     </row>
     <row r="27" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A27" s="75" t="s">
+        <v>195</v>
+      </c>
+      <c r="B27" s="166" t="s">
         <v>196</v>
-      </c>
-      <c r="B27" s="166" t="s">
-        <v>197</v>
       </c>
       <c r="C27" s="170"/>
       <c r="D27" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E27" s="170"/>
       <c r="F27" s="54"/>
@@ -29441,7 +29444,7 @@
       </c>
       <c r="C28" s="170"/>
       <c r="D28" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E28" s="170"/>
       <c r="F28" s="54"/>
@@ -29475,7 +29478,7 @@
       </c>
       <c r="C29" s="170"/>
       <c r="D29" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E29" s="170"/>
       <c r="F29" s="54"/>
@@ -29509,7 +29512,7 @@
       </c>
       <c r="C30" s="170"/>
       <c r="D30" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E30" s="170"/>
       <c r="F30" s="54"/>
@@ -29543,7 +29546,7 @@
       </c>
       <c r="C31" s="170"/>
       <c r="D31" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E31" s="170"/>
       <c r="F31" s="54"/>
@@ -29577,7 +29580,7 @@
       </c>
       <c r="C32" s="170"/>
       <c r="D32" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E32" s="170"/>
       <c r="F32" s="54"/>
@@ -29611,7 +29614,7 @@
       </c>
       <c r="C33" s="170"/>
       <c r="D33" s="170" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E33" s="170"/>
       <c r="F33" s="54"/>
@@ -29641,14 +29644,14 @@
         <v>15</v>
       </c>
       <c r="B34" s="168" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C34" s="170"/>
       <c r="D34" s="170" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E34" s="170" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F34" s="54"/>
       <c r="G34" s="54"/>
@@ -29681,7 +29684,7 @@
       </c>
       <c r="C35" s="170"/>
       <c r="D35" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E35" s="170"/>
       <c r="F35" s="54"/>
@@ -29715,7 +29718,7 @@
       </c>
       <c r="C36" s="170"/>
       <c r="D36" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" s="170"/>
       <c r="F36" s="54"/>
@@ -29749,7 +29752,7 @@
       </c>
       <c r="C37" s="190"/>
       <c r="D37" s="190" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E37" s="190"/>
       <c r="F37" s="111"/>
@@ -29783,7 +29786,7 @@
       </c>
       <c r="C38" s="170"/>
       <c r="D38" s="170" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E38" s="170"/>
       <c r="F38" s="54"/>
@@ -29817,7 +29820,7 @@
       </c>
       <c r="C39" s="170"/>
       <c r="D39" s="170" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E39" s="170"/>
       <c r="F39" s="54"/>
@@ -29911,7 +29914,7 @@
         <v>23</v>
       </c>
       <c r="B42" s="168" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C42" s="170"/>
       <c r="D42" s="170"/>
@@ -29943,7 +29946,7 @@
         <v>24</v>
       </c>
       <c r="B43" s="168" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C43" s="170"/>
       <c r="D43" s="170"/>
@@ -29979,7 +29982,7 @@
       </c>
       <c r="C44" s="170"/>
       <c r="D44" s="170" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E44" s="170"/>
       <c r="F44" s="54"/>
@@ -30013,7 +30016,7 @@
       </c>
       <c r="C45" s="193"/>
       <c r="D45" s="193" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E45" s="193"/>
       <c r="F45" s="194"/>
@@ -30048,7 +30051,7 @@
       <c r="C46" s="170"/>
       <c r="D46" s="170"/>
       <c r="E46" s="170" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F46" s="54"/>
       <c r="G46" s="54"/>
@@ -30109,12 +30112,12 @@
         <v>29</v>
       </c>
       <c r="B48" s="168" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C48" s="170"/>
       <c r="D48" s="170"/>
       <c r="E48" s="170" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F48" s="54"/>
       <c r="G48" s="54"/>
@@ -30138,46 +30141,46 @@
       <c r="Y48" s="54"/>
       <c r="Z48" s="54"/>
     </row>
-    <row r="49" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A49" s="174">
+    <row r="49" spans="1:26" s="73" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A49" s="188">
         <v>30</v>
       </c>
-      <c r="B49" s="168" t="s">
+      <c r="B49" s="189" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="170"/>
-      <c r="D49" s="170"/>
-      <c r="E49" s="170" t="s">
-        <v>169</v>
-      </c>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="54"/>
-      <c r="P49" s="54"/>
-      <c r="Q49" s="54"/>
-      <c r="R49" s="54"/>
-      <c r="S49" s="54"/>
-      <c r="T49" s="54"/>
-      <c r="U49" s="54"/>
-      <c r="V49" s="54"/>
-      <c r="W49" s="54"/>
-      <c r="X49" s="54"/>
-      <c r="Y49" s="54"/>
-      <c r="Z49" s="54"/>
+      <c r="C49" s="190"/>
+      <c r="D49" s="190"/>
+      <c r="E49" s="190" t="s">
+        <v>168</v>
+      </c>
+      <c r="F49" s="111"/>
+      <c r="G49" s="111"/>
+      <c r="H49" s="111"/>
+      <c r="I49" s="111"/>
+      <c r="J49" s="111"/>
+      <c r="K49" s="111"/>
+      <c r="L49" s="111"/>
+      <c r="M49" s="111"/>
+      <c r="N49" s="111"/>
+      <c r="O49" s="111"/>
+      <c r="P49" s="111"/>
+      <c r="Q49" s="111"/>
+      <c r="R49" s="111"/>
+      <c r="S49" s="111"/>
+      <c r="T49" s="111"/>
+      <c r="U49" s="111"/>
+      <c r="V49" s="111"/>
+      <c r="W49" s="111"/>
+      <c r="X49" s="111"/>
+      <c r="Y49" s="111"/>
+      <c r="Z49" s="111"/>
     </row>
     <row r="50" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A50" s="174">
         <v>31</v>
       </c>
       <c r="B50" s="168" t="s">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="C50" s="170"/>
       <c r="D50" s="170"/>
@@ -30204,44 +30207,44 @@
       <c r="Y50" s="54"/>
       <c r="Z50" s="54"/>
     </row>
-    <row r="51" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A51" s="174">
+    <row r="51" spans="1:26" s="73" customFormat="1" ht="15.45" x14ac:dyDescent="0.4">
+      <c r="A51" s="188">
         <v>32</v>
       </c>
-      <c r="B51" s="168" t="s">
-        <v>170</v>
-      </c>
-      <c r="C51" s="170"/>
-      <c r="D51" s="170"/>
-      <c r="E51" s="170"/>
-      <c r="F51" s="54"/>
-      <c r="G51" s="54"/>
-      <c r="H51" s="54"/>
-      <c r="I51" s="54"/>
-      <c r="J51" s="54"/>
-      <c r="K51" s="54"/>
-      <c r="L51" s="54"/>
-      <c r="M51" s="54"/>
-      <c r="N51" s="54"/>
-      <c r="O51" s="54"/>
-      <c r="P51" s="54"/>
-      <c r="Q51" s="54"/>
-      <c r="R51" s="54"/>
-      <c r="S51" s="54"/>
-      <c r="T51" s="54"/>
-      <c r="U51" s="54"/>
-      <c r="V51" s="54"/>
-      <c r="W51" s="54"/>
-      <c r="X51" s="54"/>
-      <c r="Y51" s="54"/>
-      <c r="Z51" s="54"/>
+      <c r="B51" s="189" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" s="190"/>
+      <c r="D51" s="190"/>
+      <c r="E51" s="190"/>
+      <c r="F51" s="111"/>
+      <c r="G51" s="111"/>
+      <c r="H51" s="111"/>
+      <c r="I51" s="111"/>
+      <c r="J51" s="111"/>
+      <c r="K51" s="111"/>
+      <c r="L51" s="111"/>
+      <c r="M51" s="111"/>
+      <c r="N51" s="111"/>
+      <c r="O51" s="111"/>
+      <c r="P51" s="111"/>
+      <c r="Q51" s="111"/>
+      <c r="R51" s="111"/>
+      <c r="S51" s="111"/>
+      <c r="T51" s="111"/>
+      <c r="U51" s="111"/>
+      <c r="V51" s="111"/>
+      <c r="W51" s="111"/>
+      <c r="X51" s="111"/>
+      <c r="Y51" s="111"/>
+      <c r="Z51" s="111"/>
     </row>
     <row r="52" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A52" s="174">
         <v>33</v>
       </c>
       <c r="B52" s="168" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C52" s="170"/>
       <c r="D52" s="170"/>
@@ -30273,7 +30276,7 @@
         <v>34</v>
       </c>
       <c r="B53" s="168" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C53" s="170"/>
       <c r="D53" s="170"/>
@@ -30301,8 +30304,12 @@
       <c r="Z53" s="54"/>
     </row>
     <row r="54" spans="1:26" ht="15.45" x14ac:dyDescent="0.4">
-      <c r="A54" s="175"/>
-      <c r="B54" s="54"/>
+      <c r="A54" s="174">
+        <v>35</v>
+      </c>
+      <c r="B54" s="168" t="s">
+        <v>209</v>
+      </c>
       <c r="C54" s="54"/>
       <c r="D54" s="54"/>
       <c r="E54" s="54"/>
@@ -57340,7 +57347,7 @@
   <sheetData>
     <row r="3" spans="1:13" ht="15.45" x14ac:dyDescent="0.4">
       <c r="A3" s="197" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3" s="198"/>
       <c r="C3" s="198"/>
@@ -57388,7 +57395,7 @@
         <v>9</v>
       </c>
       <c r="C5" s="62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" s="63"/>
       <c r="E5" s="64"/>
@@ -57409,7 +57416,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" s="69"/>
       <c r="E6" s="70"/>
@@ -57425,10 +57432,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C7" s="68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D7" s="69"/>
       <c r="E7" s="70"/>
@@ -57437,7 +57444,7 @@
       <c r="H7" s="71"/>
       <c r="I7" s="67"/>
       <c r="L7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.45" x14ac:dyDescent="0.4">
@@ -57445,10 +57452,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C8" s="68" t="s">
         <v>137</v>
-      </c>
-      <c r="C8" s="68" t="s">
-        <v>138</v>
       </c>
       <c r="D8" s="69"/>
       <c r="E8" s="70"/>
@@ -57462,10 +57469,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9" s="69"/>
       <c r="E9" s="70"/>
@@ -57473,10 +57480,10 @@
       <c r="G9" s="67"/>
       <c r="H9" s="71"/>
       <c r="I9" s="67" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L9" s="73" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M9" s="74"/>
     </row>
@@ -57490,10 +57497,10 @@
       <c r="G10" s="67"/>
       <c r="H10" s="71"/>
       <c r="I10" s="67" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L10" s="73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M10" s="74"/>
     </row>
@@ -57520,36 +57527,36 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="L14" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="M14" s="74" t="s">
         <v>155</v>
-      </c>
-      <c r="M14" s="74" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" t="s">
         <v>146</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>147</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>148</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>149</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>150</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>151</v>
       </c>
-      <c r="J15" t="s">
-        <v>152</v>
-      </c>
       <c r="L15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M15">
         <v>15</v>
@@ -57557,117 +57564,117 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="D16" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E16" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F16" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G16" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H16" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I16" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J16" s="73" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D18" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E18" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F18" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G18" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H18" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I18" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J18" s="73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="4:10" x14ac:dyDescent="0.4">
       <c r="D20" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E20" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F20" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G20" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H20" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I20" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J20" s="73" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
